--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,10 +594,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28/02/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>3 4 1 9
+0 2 8 5
+4 5 9 7
+6 1 7 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -605,14 +620,21 @@
 6 8 7 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 12/226 (5.31%)
+▶ Direct: 12/4302 (0.28%)
+▶ Total Sets hit: 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -620,7 +642,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -642,7 +664,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -664,7 +686,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -686,7 +708,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -708,7 +730,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -730,7 +752,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -752,7 +774,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -774,7 +796,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -796,7 +818,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -818,7 +840,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -840,7 +862,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -862,7 +884,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -884,7 +906,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -906,7 +928,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -928,7 +950,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -950,7 +972,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -972,7 +994,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -994,7 +1016,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1016,7 +1038,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1038,7 +1060,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1060,7 +1082,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1082,7 +1104,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1104,7 +1126,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1280,7 +1302,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1302,7 +1324,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1324,7 +1346,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1346,7 +1368,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1368,7 +1390,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1390,7 +1412,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1412,7 +1434,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1434,7 +1456,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1456,7 +1478,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1654,7 +1676,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1676,7 +1698,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1698,7 +1720,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1720,7 +1742,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1808,7 +1830,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1816,17 +1838,17 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="1" t="n"/>
-    </row>
     <row r="59">
-      <c r="B59" s="1" t="n"/>
+      <c r="B59" s="4" t="n"/>
       <c r="C59" s="1" t="n"/>
     </row>
     <row r="60">
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="1" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="1" t="n"/>
+      <c r="C61" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1839,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1867,10 +1889,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>25/02/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>8 4 1 6
+7 5 6 7
+3 8 0 5
+4 1 2 9</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 15/4302 (0.35%)
+✅ iBet: 15/226 (6.64%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -1878,20 +1921,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -1899,20 +1942,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -1920,20 +1963,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -1941,20 +1984,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -1962,20 +2005,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -1983,20 +2026,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2004,20 +2047,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2025,20 +2068,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2046,20 +2089,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2067,20 +2110,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2088,20 +2131,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2109,20 +2152,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2130,20 +2173,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2151,20 +2194,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2172,20 +2215,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2193,20 +2236,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2214,20 +2257,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2235,20 +2278,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2256,20 +2299,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2277,20 +2320,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2298,20 +2341,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2319,20 +2362,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2340,20 +2383,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2361,20 +2404,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2382,20 +2425,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2403,20 +2446,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2424,20 +2467,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2445,20 +2488,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2466,20 +2509,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2487,20 +2530,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2508,20 +2551,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2529,20 +2572,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2550,20 +2593,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2571,20 +2614,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2592,20 +2635,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2613,20 +2656,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2634,20 +2677,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2655,20 +2698,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2676,20 +2719,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2697,20 +2740,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2718,20 +2761,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2739,20 +2782,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -2760,20 +2803,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -2781,20 +2824,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -2802,20 +2845,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -2823,20 +2866,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -2844,20 +2887,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -2865,20 +2908,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -2886,20 +2929,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -2907,20 +2950,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -2928,20 +2971,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -2949,20 +2992,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -2970,20 +3013,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -2991,20 +3034,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3012,20 +3055,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3033,20 +3076,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3054,20 +3097,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3075,20 +3118,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3096,20 +3139,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3117,20 +3160,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3138,20 +3181,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3159,20 +3202,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3180,20 +3223,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3201,20 +3244,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3222,20 +3265,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3243,20 +3286,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3264,20 +3307,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3285,20 +3328,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3306,20 +3349,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3327,20 +3370,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3348,20 +3391,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3369,20 +3412,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3390,20 +3433,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3411,20 +3454,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3432,20 +3475,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3453,20 +3496,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3474,20 +3517,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3495,20 +3538,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3516,20 +3559,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3537,20 +3580,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3558,20 +3601,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3579,20 +3622,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3600,20 +3643,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3621,20 +3664,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3642,20 +3685,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3663,20 +3706,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3684,20 +3727,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3705,20 +3748,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3726,20 +3769,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -3747,20 +3790,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -3768,20 +3811,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -3789,20 +3832,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -3810,20 +3853,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -3831,20 +3874,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -3852,20 +3895,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -3873,20 +3916,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -3894,20 +3937,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -3915,20 +3958,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -3936,20 +3979,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -3957,20 +4000,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -3978,20 +4021,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -3999,20 +4042,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4020,20 +4063,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4041,20 +4084,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4062,20 +4105,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4083,20 +4126,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4104,20 +4147,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4125,20 +4168,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4146,16 +4189,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="1" t="n"/>
-      <c r="C111" s="1" t="n"/>
     </row>
     <row r="112">
       <c r="B112" s="1" t="n"/>
@@ -4167,6 +4206,7 @@
     </row>
     <row r="114">
       <c r="B114" s="1" t="n"/>
+      <c r="C114" s="1" t="n"/>
     </row>
     <row r="115">
       <c r="B115" s="1" t="n"/>
@@ -4242,6 +4282,9 @@
     </row>
     <row r="139">
       <c r="B139" s="1" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4254,7 +4297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4282,28 +4325,47 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25/02/2026 (Wed)</t>
+          <t>28/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 6437</t>
-        </is>
-      </c>
-      <c r="C2" s="23" t="inlineStr"/>
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>25/02/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7295 5263 4178 2645 6437</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4311,18 +4373,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4330,18 +4392,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4349,18 +4411,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4368,18 +4430,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4387,18 +4449,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4406,18 +4468,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4425,18 +4487,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4444,18 +4506,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4463,18 +4525,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4482,18 +4544,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4501,18 +4563,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4520,18 +4582,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4539,18 +4601,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4558,18 +4620,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4577,18 +4639,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4596,18 +4658,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4615,18 +4677,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4634,18 +4696,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4653,18 +4715,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4672,18 +4734,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4691,18 +4753,18 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4710,18 +4772,18 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4729,18 +4791,18 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4748,18 +4810,18 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4767,18 +4829,18 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4786,18 +4848,18 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4805,18 +4867,18 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4824,18 +4886,18 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4843,18 +4905,18 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>6276 7295 9746 2056 2508</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4862,18 +4924,18 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4881,18 +4943,18 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4900,18 +4962,18 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4919,18 +4981,18 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>6276 7295 9746 4748 7352</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4938,18 +5000,18 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>6276 7295 9746 7352 8590</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4957,18 +5019,18 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 4987</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4976,18 +5038,18 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 1396</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4995,18 +5057,18 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C40" s="20" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5014,18 +5076,18 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5033,18 +5095,18 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>8590 1396 9223 3378 0316</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5052,18 +5114,18 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5071,18 +5133,18 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C44" s="20" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5090,18 +5152,18 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>9223 0316 7499 8612 6456</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5109,18 +5171,18 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>9223 0316 8612 7499 6456</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5128,18 +5190,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>0316 8612 6456 7499 5548</t>
         </is>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5147,18 +5209,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>0316 6456 8612 5548 0180</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5166,18 +5228,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0316 8612 5548 0180 8989</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5185,18 +5247,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0316 8612 5548 8989 4326</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5204,18 +5266,18 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>0316 8612 5548 4326 8585</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5223,18 +5285,18 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>3378 0316 8612 5548 8585</t>
         </is>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5242,18 +5304,18 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Sun - 26/10/2025</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>0316 8612 5548 8585 4178</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5261,18 +5323,18 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Sat - 25/10/2025</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>8612 5548 8585 6143 8729</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5280,18 +5342,18 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/02/2026 (Sat)</t>
+          <t>01/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
@@ -609,10 +609,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28/02/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>3 4 1 9
+0 2 8 5
+4 5 9 7
+6 1 7 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 10/226 (4.42%)
+▶ Direct: 10/4302 (0.23%)
+▶ Total Sets hit: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -620,7 +642,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -642,7 +664,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -664,7 +686,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -686,7 +708,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -708,7 +730,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -730,7 +752,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -752,7 +774,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -774,7 +796,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -796,7 +818,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -818,7 +840,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -840,7 +862,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -862,7 +884,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -884,7 +906,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -906,7 +928,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -928,7 +950,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -950,7 +972,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -972,7 +994,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -994,7 +1016,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1016,7 +1038,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1038,7 +1060,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1060,7 +1082,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1082,7 +1104,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1104,7 +1126,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1302,7 +1324,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1324,7 +1346,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1346,7 +1368,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1368,7 +1390,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1390,7 +1412,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1412,7 +1434,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1434,7 +1456,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1456,7 +1478,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1676,7 +1698,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1698,7 +1720,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1720,7 +1742,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1742,7 +1764,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1830,7 +1852,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1838,17 +1860,17 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="1" t="n"/>
-    </row>
     <row r="60">
-      <c r="B60" s="1" t="n"/>
+      <c r="B60" s="4" t="n"/>
       <c r="C60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="1" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="1" t="n"/>
+      <c r="C62" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1861,7 +1883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1889,10 +1911,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28/02/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>4 4 0 2
+0 1 3 1
+7 5 9 6
+5 2 8 7</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 10/3864 (0.26%)
+✅ iBet: 10/208 (4.81%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -1900,20 +1943,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -1921,20 +1964,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -1942,20 +1985,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -1963,20 +2006,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -1984,20 +2027,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2005,20 +2048,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2026,20 +2069,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2047,20 +2090,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2068,20 +2111,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2089,20 +2132,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2110,20 +2153,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2131,20 +2174,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2152,20 +2195,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2173,20 +2216,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2194,20 +2237,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2215,20 +2258,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2236,20 +2279,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2257,20 +2300,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2278,20 +2321,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2299,20 +2342,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2320,20 +2363,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2341,20 +2384,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2362,20 +2405,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2383,20 +2426,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2404,20 +2447,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2425,20 +2468,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2446,20 +2489,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2467,20 +2510,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2488,20 +2531,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2509,20 +2552,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2530,20 +2573,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2551,20 +2594,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2572,20 +2615,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2593,20 +2636,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2614,20 +2657,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2635,20 +2678,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2656,20 +2699,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2677,20 +2720,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2698,20 +2741,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2719,20 +2762,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2740,20 +2783,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2761,20 +2804,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2782,20 +2825,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -2803,20 +2846,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -2824,20 +2867,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -2845,20 +2888,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -2866,20 +2909,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -2887,20 +2930,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -2908,20 +2951,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -2929,20 +2972,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -2950,20 +2993,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -2971,20 +3014,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -2992,20 +3035,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3013,20 +3056,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3034,20 +3077,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3055,20 +3098,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3076,20 +3119,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3097,20 +3140,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3118,20 +3161,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3139,20 +3182,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3160,20 +3203,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3181,20 +3224,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3202,20 +3245,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3223,20 +3266,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3244,20 +3287,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3265,20 +3308,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3286,20 +3329,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3307,20 +3350,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3328,20 +3371,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3349,20 +3392,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3370,20 +3413,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3391,20 +3434,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3412,20 +3455,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3433,20 +3476,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3454,20 +3497,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3475,20 +3518,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3496,20 +3539,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3517,20 +3560,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3538,20 +3581,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3559,20 +3602,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3580,20 +3623,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3601,20 +3644,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3622,20 +3665,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3643,20 +3686,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3664,20 +3707,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3685,20 +3728,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3706,20 +3749,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3727,20 +3770,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3748,20 +3791,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3769,20 +3812,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -3790,20 +3833,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -3811,20 +3854,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -3832,20 +3875,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -3853,20 +3896,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -3874,20 +3917,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -3895,20 +3938,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -3916,20 +3959,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -3937,20 +3980,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -3958,20 +4001,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -3979,20 +4022,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4000,20 +4043,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4021,20 +4064,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4042,20 +4085,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4063,20 +4106,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4084,20 +4127,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4105,20 +4148,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4126,20 +4169,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4147,20 +4190,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4168,20 +4211,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4189,16 +4232,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="1" t="n"/>
-      <c r="C112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="B113" s="1" t="n"/>
@@ -4210,6 +4249,7 @@
     </row>
     <row r="115">
       <c r="B115" s="1" t="n"/>
+      <c r="C115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="B116" s="1" t="n"/>
@@ -4285,6 +4325,9 @@
     </row>
     <row r="140">
       <c r="B140" s="1" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4297,7 +4340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4325,7 +4368,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28/02/2026 (Sat)</t>
+          <t>01/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4333,20 +4376,39 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr"/>
+      <c r="C2" s="19" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28/02/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4354,18 +4416,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4373,18 +4435,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4392,18 +4454,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4411,18 +4473,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4430,18 +4492,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4449,18 +4511,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4468,18 +4530,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4487,18 +4549,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4506,18 +4568,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4525,18 +4587,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4544,18 +4606,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4563,18 +4625,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4582,18 +4644,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4601,18 +4663,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4620,18 +4682,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4639,18 +4701,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4658,18 +4720,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4677,18 +4739,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4696,18 +4758,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4715,18 +4777,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4734,18 +4796,18 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4753,18 +4815,18 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4772,18 +4834,18 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4791,18 +4853,18 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4810,18 +4872,18 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4829,18 +4891,18 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4848,18 +4910,18 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4867,18 +4929,18 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4886,18 +4948,18 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4905,18 +4967,18 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>6276 7295 9746 2056 2508</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4924,18 +4986,18 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4943,18 +5005,18 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4962,18 +5024,18 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4981,18 +5043,18 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>6276 7295 9746 4748 7352</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5000,18 +5062,18 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>6276 7295 9746 7352 8590</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5019,18 +5081,18 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 4987</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5038,18 +5100,18 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 1396</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5057,18 +5119,18 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5076,18 +5138,18 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5095,18 +5157,18 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>8590 1396 9223 3378 0316</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5114,18 +5176,18 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C44" s="22" t="inlineStr">
+      <c r="C45" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5133,18 +5195,18 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5152,18 +5214,18 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>9223 0316 7499 8612 6456</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5171,18 +5233,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>9223 0316 8612 7499 6456</t>
         </is>
       </c>
-      <c r="C47" s="16" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5190,18 +5252,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>0316 8612 6456 7499 5548</t>
         </is>
       </c>
-      <c r="C48" s="22" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5209,18 +5271,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0316 6456 8612 5548 0180</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5228,18 +5290,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0316 8612 5548 0180 8989</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5247,18 +5309,18 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>0316 8612 5548 8989 4326</t>
         </is>
       </c>
-      <c r="C51" s="16" t="inlineStr">
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5266,18 +5328,18 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>0316 8612 5548 4326 8585</t>
         </is>
       </c>
-      <c r="C52" s="22" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5285,18 +5347,18 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>3378 0316 8612 5548 8585</t>
         </is>
       </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5304,18 +5366,18 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Sun - 26/10/2025</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>0316 8612 5548 8585 4178</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5323,18 +5385,18 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Sat - 25/10/2025</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>8612 5548 8585 6143 8729</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5342,18 +5404,18 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,10 +594,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>04/03/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>8 4 1 7
+0 2 8 5
+4 5 9 3
+6 9 7 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -605,14 +620,21 @@
 6 1 7 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 17/226 (7.52%)
+▶ Direct: 17/4302 (0.40%)
+▶ Total Sets hit: 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -620,7 +642,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -642,7 +664,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -664,7 +686,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -686,7 +708,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -708,7 +730,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -730,7 +752,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -752,7 +774,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -774,7 +796,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -796,7 +818,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -818,7 +840,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -840,7 +862,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -862,7 +884,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -884,7 +906,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -906,7 +928,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -928,7 +950,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -950,7 +972,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -972,7 +994,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -994,7 +1016,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1016,7 +1038,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1038,7 +1060,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1060,7 +1082,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1082,7 +1104,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1104,7 +1126,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1324,7 +1346,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1346,7 +1368,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1368,7 +1390,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1390,7 +1412,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1412,7 +1434,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1434,7 +1456,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1456,7 +1478,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1478,7 +1500,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1698,7 +1720,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1720,7 +1742,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1764,7 +1786,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1830,7 +1852,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1852,7 +1874,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1860,17 +1882,17 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="1" t="n"/>
-    </row>
     <row r="61">
-      <c r="B61" s="1" t="n"/>
+      <c r="B61" s="4" t="n"/>
       <c r="C61" s="1" t="n"/>
     </row>
     <row r="62">
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="1" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="1" t="n"/>
+      <c r="C63" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1883,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1911,10 +1933,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>7 6 9 7
+1 8 0 8
+2 9 5 3
+0 3 1 4</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 13/4230 (0.31%)
+✅ iBet: 13/221 (5.88%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -1922,20 +1965,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -1943,20 +1986,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -1964,20 +2007,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -1985,20 +2028,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2006,20 +2049,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2027,20 +2070,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2048,20 +2091,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2069,20 +2112,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2090,20 +2133,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2111,20 +2154,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2132,20 +2175,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2153,20 +2196,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2174,20 +2217,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2195,20 +2238,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2216,20 +2259,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2237,20 +2280,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2258,20 +2301,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2279,20 +2322,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2300,20 +2343,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2321,20 +2364,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2342,20 +2385,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2363,20 +2406,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2384,20 +2427,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2405,20 +2448,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2426,20 +2469,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2447,20 +2490,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2468,20 +2511,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2489,20 +2532,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2510,20 +2553,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2531,20 +2574,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2552,20 +2595,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2573,20 +2616,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2594,20 +2637,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2615,20 +2658,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2636,20 +2679,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2657,20 +2700,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2678,20 +2721,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2699,20 +2742,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2720,20 +2763,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2741,20 +2784,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2762,20 +2805,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2783,20 +2826,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2804,20 +2847,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2825,20 +2868,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -2846,20 +2889,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -2867,20 +2910,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -2888,20 +2931,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -2909,20 +2952,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -2930,20 +2973,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -2951,20 +2994,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -2972,20 +3015,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -2993,20 +3036,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3014,20 +3057,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3035,20 +3078,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3056,20 +3099,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3077,20 +3120,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3098,20 +3141,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3119,20 +3162,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3140,20 +3183,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3161,20 +3204,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3182,20 +3225,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3203,20 +3246,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3224,20 +3267,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3245,20 +3288,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3266,20 +3309,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3287,20 +3330,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3308,20 +3351,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3329,20 +3372,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3350,20 +3393,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3371,20 +3414,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3392,20 +3435,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3413,20 +3456,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3434,20 +3477,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3455,20 +3498,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3476,20 +3519,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3497,20 +3540,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3518,20 +3561,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3539,20 +3582,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3560,20 +3603,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3581,20 +3624,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3602,20 +3645,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3623,20 +3666,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3644,20 +3687,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3665,20 +3708,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3686,20 +3729,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3707,20 +3750,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3728,20 +3771,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3749,20 +3792,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3770,20 +3813,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3791,20 +3834,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3812,20 +3855,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -3833,20 +3876,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -3854,20 +3897,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -3875,20 +3918,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -3896,20 +3939,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -3917,20 +3960,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -3938,20 +3981,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -3959,20 +4002,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -3980,20 +4023,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4001,20 +4044,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4022,20 +4065,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4043,20 +4086,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4064,20 +4107,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4085,20 +4128,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4106,20 +4149,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4127,20 +4170,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4148,20 +4191,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4169,20 +4212,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4190,20 +4233,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4211,20 +4254,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4232,16 +4275,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="1" t="n"/>
-      <c r="C113" s="1" t="n"/>
     </row>
     <row r="114">
       <c r="B114" s="1" t="n"/>
@@ -4253,6 +4292,7 @@
     </row>
     <row r="116">
       <c r="B116" s="1" t="n"/>
+      <c r="C116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="B117" s="1" t="n"/>
@@ -4328,6 +4368,9 @@
     </row>
     <row r="141">
       <c r="B141" s="1" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4340,7 +4383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4368,7 +4411,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4376,20 +4419,39 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr"/>
+      <c r="C2" s="21" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4397,18 +4459,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4416,18 +4478,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4435,18 +4497,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4454,18 +4516,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4473,18 +4535,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4492,18 +4554,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4511,18 +4573,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4530,18 +4592,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4549,18 +4611,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4568,18 +4630,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4587,18 +4649,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4606,18 +4668,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4625,18 +4687,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4644,18 +4706,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4663,18 +4725,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4682,18 +4744,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4701,18 +4763,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4720,18 +4782,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4739,18 +4801,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4758,18 +4820,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4777,18 +4839,18 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4796,18 +4858,18 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4815,18 +4877,18 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4834,18 +4896,18 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C28" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4853,18 +4915,18 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C29" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4872,18 +4934,18 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4891,18 +4953,18 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4910,18 +4972,18 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4929,18 +4991,18 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4948,18 +5010,18 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4967,18 +5029,18 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>6276 7295 9746 2056 2508</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4986,18 +5048,18 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5005,18 +5067,18 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5024,18 +5086,18 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5043,18 +5105,18 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>6276 7295 9746 4748 7352</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C39" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5062,18 +5124,18 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>6276 7295 9746 7352 8590</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5081,18 +5143,18 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 4987</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5100,18 +5162,18 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 1396</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5119,18 +5181,18 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5138,18 +5200,18 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5157,18 +5219,18 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>8590 1396 9223 3378 0316</t>
         </is>
       </c>
-      <c r="C44" s="16" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5176,18 +5238,18 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C45" s="22" t="inlineStr">
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5195,18 +5257,18 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5214,18 +5276,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>9223 0316 7499 8612 6456</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5233,18 +5295,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>9223 0316 8612 7499 6456</t>
         </is>
       </c>
-      <c r="C48" s="16" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5252,18 +5314,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0316 8612 6456 7499 5548</t>
         </is>
       </c>
-      <c r="C49" s="22" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5271,18 +5333,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0316 6456 8612 5548 0180</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5290,18 +5352,18 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>0316 8612 5548 0180 8989</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5309,18 +5371,18 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>0316 8612 5548 8989 4326</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5328,18 +5390,18 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>0316 8612 5548 4326 8585</t>
         </is>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5347,18 +5409,18 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>3378 0316 8612 5548 8585</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C55" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5366,18 +5428,18 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Sun - 26/10/2025</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>0316 8612 5548 8585 4178</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5385,18 +5447,18 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Sat - 25/10/2025</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>8612 5548 8585 6143 8729</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5404,18 +5466,18 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C58" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
@@ -609,10 +609,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>04/03/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>8 4 1 7
+0 2 8 5
+4 5 9 3
+6 9 7 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 12/237 (5.06%)
+▶ Direct: 13/4554 (0.29%)
+▶ Total Sets hit: 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -620,7 +642,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -642,7 +664,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -664,7 +686,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -686,7 +708,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -708,7 +730,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -730,7 +752,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -752,7 +774,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -774,7 +796,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -796,7 +818,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -818,7 +840,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -840,7 +862,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -862,7 +884,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -884,7 +906,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -906,7 +928,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -928,7 +950,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -950,7 +972,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -972,7 +994,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -994,7 +1016,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1016,7 +1038,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1038,7 +1060,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1060,7 +1082,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1082,7 +1104,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1104,7 +1126,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1324,7 +1346,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1346,7 +1368,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1368,7 +1390,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1390,7 +1412,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1412,7 +1434,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1434,7 +1456,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1456,7 +1478,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1500,7 +1522,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1698,7 +1720,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1720,7 +1742,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1786,7 +1808,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1830,7 +1852,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1852,7 +1874,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1860,13 +1882,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1874,7 +1896,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1882,17 +1904,17 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="1" t="n"/>
-    </row>
     <row r="62">
-      <c r="B62" s="1" t="n"/>
+      <c r="B62" s="4" t="n"/>
       <c r="C62" s="1" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="1" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="1" t="n"/>
+      <c r="C64" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1905,7 +1927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1933,10 +1955,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>04/03/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>1 1 0 4
+3 2 9 8
+5 3 2 9
+7 6 8 7</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 10/4230 (0.24%)
+✅ iBet: 10/221 (4.52%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -1944,20 +1987,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -1965,20 +2008,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -1986,20 +2029,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -2007,20 +2050,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -2028,20 +2071,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2049,20 +2092,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2070,20 +2113,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2091,20 +2134,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2112,20 +2155,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2133,20 +2176,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2154,20 +2197,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2175,20 +2218,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2196,20 +2239,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2217,20 +2260,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2238,20 +2281,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2259,20 +2302,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2280,20 +2323,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2301,20 +2344,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2322,20 +2365,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2343,20 +2386,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2364,20 +2407,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2385,20 +2428,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2406,20 +2449,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2427,20 +2470,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2448,20 +2491,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2469,20 +2512,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2490,20 +2533,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2511,20 +2554,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2532,20 +2575,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2553,20 +2596,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2574,20 +2617,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2595,20 +2638,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2616,20 +2659,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2637,20 +2680,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2658,20 +2701,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2679,20 +2722,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2700,20 +2743,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2721,20 +2764,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2742,20 +2785,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2763,20 +2806,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2784,20 +2827,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2805,20 +2848,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2826,20 +2869,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2847,20 +2890,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2868,20 +2911,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -2889,20 +2932,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -2910,20 +2953,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -2931,20 +2974,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -2952,20 +2995,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -2973,20 +3016,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -2994,20 +3037,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -3015,20 +3058,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -3036,20 +3079,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3057,20 +3100,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3078,20 +3121,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3099,20 +3142,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3120,20 +3163,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3141,20 +3184,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3162,20 +3205,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3183,20 +3226,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3204,20 +3247,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3225,20 +3268,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3246,20 +3289,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3267,20 +3310,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3288,20 +3331,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3309,20 +3352,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3330,20 +3373,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3351,20 +3394,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3372,20 +3415,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3393,20 +3436,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3414,20 +3457,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3435,20 +3478,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3456,20 +3499,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3477,20 +3520,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3498,20 +3541,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3519,20 +3562,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3540,20 +3583,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3561,20 +3604,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3582,20 +3625,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3603,20 +3646,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3624,20 +3667,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3645,20 +3688,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3666,20 +3709,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3687,20 +3730,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3708,20 +3751,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3729,20 +3772,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3750,20 +3793,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3771,20 +3814,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3792,20 +3835,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3813,20 +3856,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3834,20 +3877,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3855,20 +3898,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -3876,20 +3919,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -3897,20 +3940,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -3918,20 +3961,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -3939,20 +3982,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -3960,20 +4003,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -3981,20 +4024,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -4002,20 +4045,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -4023,20 +4066,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4044,20 +4087,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4065,20 +4108,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4086,20 +4129,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4107,20 +4150,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4128,20 +4171,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4149,20 +4192,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4170,20 +4213,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4191,20 +4234,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4212,20 +4255,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4233,20 +4276,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4254,20 +4297,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4275,16 +4318,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="1" t="n"/>
-      <c r="C114" s="1" t="n"/>
     </row>
     <row r="115">
       <c r="B115" s="1" t="n"/>
@@ -4296,6 +4335,7 @@
     </row>
     <row r="117">
       <c r="B117" s="1" t="n"/>
+      <c r="C117" s="1" t="n"/>
     </row>
     <row r="118">
       <c r="B118" s="1" t="n"/>
@@ -4371,6 +4411,9 @@
     </row>
     <row r="142">
       <c r="B142" s="1" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4383,7 +4426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4411,7 +4454,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4419,12 +4462,12 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr"/>
+      <c r="C2" s="23" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4432,7 +4475,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4443,15 +4486,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4459,18 +4521,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4478,18 +4540,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4497,18 +4559,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4516,18 +4578,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4535,18 +4597,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4554,18 +4616,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4573,18 +4635,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4592,18 +4654,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4611,18 +4673,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4630,18 +4692,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4649,18 +4711,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4668,18 +4730,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4687,18 +4749,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4706,18 +4768,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4725,18 +4787,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4744,18 +4806,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4763,18 +4825,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4782,18 +4844,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4801,18 +4863,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4820,18 +4882,18 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4839,18 +4901,18 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4858,18 +4920,18 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4877,18 +4939,18 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4896,18 +4958,18 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4915,18 +4977,18 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4934,18 +4996,18 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4953,18 +5015,18 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4972,18 +5034,18 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4991,18 +5053,18 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5010,18 +5072,18 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5029,18 +5091,18 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>6276 7295 9746 2056 2508</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5048,18 +5110,18 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5067,18 +5129,18 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5086,18 +5148,18 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5105,18 +5167,18 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>6276 7295 9746 4748 7352</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C40" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5124,18 +5186,18 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>6276 7295 9746 7352 8590</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5143,18 +5205,18 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 4987</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5162,18 +5224,18 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 1396</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5181,18 +5243,18 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5200,18 +5262,18 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5219,18 +5281,18 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>8590 1396 9223 3378 0316</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5238,18 +5300,18 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5257,18 +5319,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5276,18 +5338,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>9223 0316 7499 8612 6456</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5295,18 +5357,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>9223 0316 8612 7499 6456</t>
         </is>
       </c>
-      <c r="C49" s="16" t="inlineStr">
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5314,18 +5376,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>0316 8612 6456 7499 5548</t>
         </is>
       </c>
-      <c r="C50" s="22" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5333,18 +5395,18 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>0316 6456 8612 5548 0180</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5352,18 +5414,18 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>0316 8612 5548 0180 8989</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5371,18 +5433,18 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>0316 8612 5548 8989 4326</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5390,18 +5452,18 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>0316 8612 5548 4326 8585</t>
         </is>
       </c>
-      <c r="C54" s="22" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5409,18 +5471,18 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>3378 0316 8612 5548 8585</t>
         </is>
       </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="C56" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5428,18 +5490,18 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Sun - 26/10/2025</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>0316 8612 5548 8585 4178</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5447,18 +5509,18 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Sat - 25/10/2025</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>8612 5548 8585 6143 8729</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5466,18 +5528,18 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>08/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
@@ -622,19 +622,41 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>▶ iBet: 9/237 (3.80%)
+▶ Direct: 9/4554 (0.20%)
+▶ Total Sets hit: 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>04/03/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>8 4 1 7
+0 2 8 5
+4 5 9 3
+6 9 7 0</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
 ▶ Total Sets hit: 13</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -642,7 +664,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -664,7 +686,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -686,7 +708,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -708,7 +730,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -730,7 +752,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -752,7 +774,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -774,7 +796,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -796,7 +818,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -818,7 +840,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -840,7 +862,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -862,7 +884,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -884,7 +906,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -906,7 +928,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -928,7 +950,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -950,7 +972,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -972,7 +994,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -994,7 +1016,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1016,7 +1038,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1038,7 +1060,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1060,7 +1082,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1082,7 +1104,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1104,7 +1126,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1324,7 +1346,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1346,7 +1368,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1368,7 +1390,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1390,7 +1412,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1412,7 +1434,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1434,7 +1456,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1456,7 +1478,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1522,7 +1544,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1698,7 +1720,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1720,7 +1742,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1808,7 +1830,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1830,7 +1852,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1852,7 +1874,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1860,13 +1882,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1874,7 +1896,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1882,13 +1904,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1896,7 +1918,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1904,17 +1926,17 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="1" t="n"/>
-    </row>
     <row r="63">
-      <c r="B63" s="1" t="n"/>
+      <c r="B63" s="4" t="n"/>
       <c r="C63" s="1" t="n"/>
     </row>
     <row r="64">
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="1" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="1" t="n"/>
+      <c r="C65" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1927,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1955,10 +1977,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07/03/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>4 2 5 6
+9 3 8 3
+1 4 7 7
+6 0 2 1</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 14/4302 (0.33%)
+✅ iBet: 14/226 (6.19%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -1966,20 +2009,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -1987,20 +2030,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -2008,20 +2051,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -2029,20 +2072,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -2050,20 +2093,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -2071,20 +2114,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2092,20 +2135,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2113,20 +2156,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2134,20 +2177,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2155,20 +2198,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2176,20 +2219,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2197,20 +2240,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2218,20 +2261,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2239,20 +2282,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2260,20 +2303,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2281,20 +2324,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2302,20 +2345,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2323,20 +2366,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2344,20 +2387,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2365,20 +2408,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2386,20 +2429,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2407,20 +2450,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2428,20 +2471,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2449,20 +2492,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2470,20 +2513,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2491,20 +2534,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2512,20 +2555,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2533,20 +2576,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2554,20 +2597,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2575,20 +2618,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2596,20 +2639,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2617,20 +2660,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2638,20 +2681,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2659,20 +2702,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2680,20 +2723,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2701,20 +2744,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2722,20 +2765,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2743,20 +2786,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2764,20 +2807,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2785,20 +2828,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2806,20 +2849,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2827,20 +2870,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2848,20 +2891,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2869,20 +2912,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2890,20 +2933,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2911,20 +2954,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -2932,20 +2975,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -2953,20 +2996,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -2974,20 +3017,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -2995,20 +3038,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -3016,20 +3059,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -3037,20 +3080,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -3058,20 +3101,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -3079,20 +3122,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3100,20 +3143,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3121,20 +3164,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3142,20 +3185,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3163,20 +3206,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3184,20 +3227,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3205,20 +3248,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3226,20 +3269,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3247,20 +3290,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3268,20 +3311,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3289,20 +3332,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3310,20 +3353,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3331,20 +3374,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3352,20 +3395,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3373,20 +3416,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3394,20 +3437,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3415,20 +3458,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3436,20 +3479,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3457,20 +3500,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3478,20 +3521,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3499,20 +3542,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3520,20 +3563,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3541,20 +3584,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3562,20 +3605,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3583,20 +3626,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3604,20 +3647,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3625,20 +3668,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3646,20 +3689,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3667,20 +3710,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3688,20 +3731,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3709,20 +3752,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3730,20 +3773,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3751,20 +3794,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3772,20 +3815,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3793,20 +3836,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3814,20 +3857,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3835,20 +3878,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3856,20 +3899,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3877,20 +3920,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3898,20 +3941,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -3919,20 +3962,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -3940,20 +3983,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -3961,20 +4004,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -3982,20 +4025,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -4003,20 +4046,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -4024,20 +4067,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -4045,20 +4088,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -4066,20 +4109,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4087,20 +4130,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4108,20 +4151,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4129,20 +4172,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4150,20 +4193,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4171,20 +4214,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4192,20 +4235,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4213,20 +4256,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4234,20 +4277,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4255,20 +4298,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4276,20 +4319,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4297,20 +4340,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4318,16 +4361,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="1" t="n"/>
-      <c r="C115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="B116" s="1" t="n"/>
@@ -4339,6 +4378,7 @@
     </row>
     <row r="118">
       <c r="B118" s="1" t="n"/>
+      <c r="C118" s="1" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="1" t="n"/>
@@ -4414,6 +4454,9 @@
     </row>
     <row r="143">
       <c r="B143" s="1" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4426,7 +4469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4454,7 +4497,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>08/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4462,12 +4505,12 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr"/>
+      <c r="C2" s="17" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4475,7 +4518,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4486,7 +4529,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4494,7 +4537,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4505,15 +4548,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4521,18 +4583,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4540,18 +4602,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4559,18 +4621,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4578,18 +4640,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4597,18 +4659,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4616,18 +4678,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4635,18 +4697,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4654,18 +4716,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4673,18 +4735,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4692,18 +4754,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4711,18 +4773,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4730,18 +4792,18 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4749,18 +4811,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4768,18 +4830,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4787,18 +4849,18 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4806,18 +4868,18 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4825,18 +4887,18 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4844,18 +4906,18 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4863,18 +4925,18 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4882,18 +4944,18 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4901,18 +4963,18 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4920,18 +4982,18 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4939,18 +5001,18 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4958,18 +5020,18 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C30" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4977,18 +5039,18 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -4996,18 +5058,18 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5015,18 +5077,18 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5034,18 +5096,18 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5053,18 +5115,18 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5072,18 +5134,18 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5091,18 +5153,18 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>6276 7295 9746 2056 2508</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5110,18 +5172,18 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5129,18 +5191,18 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5148,18 +5210,18 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5167,18 +5229,18 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>6276 7295 9746 4748 7352</t>
         </is>
       </c>
-      <c r="C40" s="20" t="inlineStr">
+      <c r="C41" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5186,18 +5248,18 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>6276 7295 9746 7352 8590</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5205,18 +5267,18 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 4987</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5224,18 +5286,18 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>6276 7295 7352 8590 1396</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5243,18 +5305,18 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C44" s="20" t="inlineStr">
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5262,18 +5324,18 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5281,18 +5343,18 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>8590 1396 9223 3378 0316</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5300,18 +5362,18 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C47" s="22" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5319,18 +5381,18 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5338,18 +5400,18 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>9223 0316 7499 8612 6456</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5357,18 +5419,18 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>9223 0316 8612 7499 6456</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5376,18 +5438,18 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>0316 8612 6456 7499 5548</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5395,18 +5457,18 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>0316 6456 8612 5548 0180</t>
         </is>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5414,18 +5476,18 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>0316 8612 5548 0180 8989</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5433,18 +5495,18 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>0316 8612 5548 8989 4326</t>
         </is>
       </c>
-      <c r="C54" s="16" t="inlineStr">
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5452,18 +5514,18 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>0316 8612 5548 4326 8585</t>
         </is>
       </c>
-      <c r="C55" s="22" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5471,18 +5533,18 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>3378 0316 8612 5548 8585</t>
         </is>
       </c>
-      <c r="C56" s="20" t="inlineStr">
+      <c r="C57" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5490,18 +5552,18 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Sun - 26/10/2025</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>0316 8612 5548 8585 4178</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5509,18 +5571,18 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Sat - 25/10/2025</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>8612 5548 8585 6143 8729</t>
         </is>
       </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="C59" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
@@ -5528,18 +5590,18 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,10 +594,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>11/03/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>8 4 1 7
+0 2 8 6
+4 5 9 3
+5 6 7 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -605,14 +620,21 @@
 6 9 7 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 11/237 (4.64%)
+▶ Direct: 12/4554 (0.26%)
+▶ Total Sets hit: 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -620,7 +642,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -642,7 +664,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -664,7 +686,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -686,7 +708,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -708,7 +730,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -730,7 +752,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -752,7 +774,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -774,7 +796,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -796,7 +818,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -818,7 +840,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -840,7 +862,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -862,7 +884,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -884,7 +906,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -906,7 +928,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -928,7 +950,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -950,7 +972,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -972,7 +994,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -994,7 +1016,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1016,7 +1038,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1038,7 +1060,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1060,7 +1082,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1082,7 +1104,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1104,7 +1126,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1324,7 +1346,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1346,7 +1368,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1368,7 +1390,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1390,7 +1412,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1412,7 +1434,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1434,7 +1456,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1456,7 +1478,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1544,7 +1566,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1698,7 +1720,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1720,7 +1742,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1830,7 +1852,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1852,7 +1874,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1860,13 +1882,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1874,7 +1896,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1882,13 +1904,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1896,7 +1918,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1904,13 +1926,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1918,7 +1940,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1926,17 +1948,17 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="1" t="n"/>
-    </row>
     <row r="64">
-      <c r="B64" s="1" t="n"/>
+      <c r="B64" s="4" t="n"/>
       <c r="C64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="1" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="1" t="n"/>
+      <c r="C66" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1949,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1977,10 +1999,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>6 5 7 7
+0 3 3 6
+1 9 8 4
+4 2 2 0</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 9/3672 (0.25%)
+✅ iBet: 9/195 (4.62%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -1988,20 +2031,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -2009,20 +2052,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -2030,20 +2073,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -2051,20 +2094,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -2072,20 +2115,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -2093,20 +2136,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -2114,20 +2157,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2135,20 +2178,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2156,20 +2199,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2177,20 +2220,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2198,20 +2241,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2219,20 +2262,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2240,20 +2283,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2261,20 +2304,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2282,20 +2325,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2303,20 +2346,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2324,20 +2367,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2345,20 +2388,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2366,20 +2409,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2387,20 +2430,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2408,20 +2451,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2429,20 +2472,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2450,20 +2493,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2471,20 +2514,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2492,20 +2535,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2513,20 +2556,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2534,20 +2577,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2555,20 +2598,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2576,20 +2619,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2597,20 +2640,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2618,20 +2661,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2639,20 +2682,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2660,20 +2703,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2681,20 +2724,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2702,20 +2745,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2723,20 +2766,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2744,20 +2787,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2765,20 +2808,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2786,20 +2829,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2807,20 +2850,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2828,20 +2871,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2849,20 +2892,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2870,20 +2913,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2891,20 +2934,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2912,20 +2955,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2933,20 +2976,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2954,20 +2997,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -2975,20 +3018,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -2996,20 +3039,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -3017,20 +3060,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -3038,20 +3081,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -3059,20 +3102,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -3080,20 +3123,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -3101,20 +3144,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -3122,20 +3165,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3143,20 +3186,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3164,20 +3207,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3185,20 +3228,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3206,20 +3249,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3227,20 +3270,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3248,20 +3291,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3269,20 +3312,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3290,20 +3333,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3311,20 +3354,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3332,20 +3375,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3353,20 +3396,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3374,20 +3417,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3395,20 +3438,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3416,20 +3459,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3437,20 +3480,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3458,20 +3501,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3479,20 +3522,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3500,20 +3543,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3521,20 +3564,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3542,20 +3585,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3563,20 +3606,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3584,20 +3627,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3605,20 +3648,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3626,20 +3669,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3647,20 +3690,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3668,20 +3711,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3689,20 +3732,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3710,20 +3753,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3731,20 +3774,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3752,20 +3795,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3773,20 +3816,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3794,20 +3837,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3815,20 +3858,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3836,20 +3879,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3857,20 +3900,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3878,20 +3921,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3899,20 +3942,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3920,20 +3963,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3941,20 +3984,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -3962,20 +4005,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -3983,20 +4026,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -4004,20 +4047,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -4025,20 +4068,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -4046,20 +4089,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -4067,20 +4110,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -4088,20 +4131,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -4109,20 +4152,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4130,20 +4173,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4151,20 +4194,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4172,20 +4215,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4193,20 +4236,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4214,20 +4257,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4235,20 +4278,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4256,20 +4299,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4277,20 +4320,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4298,20 +4341,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4319,20 +4362,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4340,20 +4383,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4361,16 +4404,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="1" t="n"/>
-      <c r="C116" s="1" t="n"/>
     </row>
     <row r="117">
       <c r="B117" s="1" t="n"/>
@@ -4382,6 +4421,7 @@
     </row>
     <row r="119">
       <c r="B119" s="1" t="n"/>
+      <c r="C119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="B120" s="1" t="n"/>
@@ -4457,6 +4497,9 @@
     </row>
     <row r="144">
       <c r="B144" s="1" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4469,7 +4512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4497,7 +4540,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/03/2026 (Sun)</t>
+          <t>11/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4505,12 +4548,12 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr"/>
+      <c r="C2" s="19" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>08/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4518,7 +4561,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4529,7 +4572,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4537,7 +4580,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4548,7 +4591,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4556,7 +4599,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4567,7 +4610,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28/02/2026 (Sat)</t>
+          <t>01/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4575,9 +4618,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4586,17 +4629,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25/02/2026 (Wed)</t>
+          <t>28/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 6437</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4605,7 +4648,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22/02/2026 (Sun)</t>
+          <t>25/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4613,9 +4656,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4624,7 +4667,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21/02/2026 (Sat)</t>
+          <t>22/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4632,9 +4675,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4643,17 +4686,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18/02/2026 (Wed)</t>
+          <t>21/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 7352</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
+          <t>7295 5263 4178 2645 6437</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4662,7 +4705,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15/02/2026 (Sun)</t>
+          <t>18/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4670,9 +4713,9 @@
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4681,15 +4724,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14/02/2026 (Sat)</t>
+          <t>15/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7295 5263 4178 7352 8612</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+          <t>7295 5263 4178 2645 7352</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4700,7 +4743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11/02/2026 (Wed)</t>
+          <t>14/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4708,7 +4751,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4719,7 +4762,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/02/2026 (Sun)</t>
+          <t>11/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4727,7 +4770,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4738,7 +4781,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/02/2026 (Sat)</t>
+          <t>08/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4746,7 +4789,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4757,7 +4800,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04/02/2026 (Wed)</t>
+          <t>07/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4765,7 +4808,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4776,7 +4819,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01/02/2026 (Sun)</t>
+          <t>04/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4784,7 +4827,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4795,7 +4838,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31/01/2026 (Sat)</t>
+          <t>01/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4803,7 +4846,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4814,7 +4857,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28/01/2026 (Wed)</t>
+          <t>31/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4822,7 +4865,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4833,7 +4876,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25/01/2026 (Sun)</t>
+          <t>28/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4841,7 +4884,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4852,15 +4895,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24/01/2026 (Sat)</t>
+          <t>25/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 2694</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+          <t>7295 5263 4178 7352 8612</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4871,7 +4914,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21/01/2026 (Wed)</t>
+          <t>24/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4879,7 +4922,7 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4890,7 +4933,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18/01/2026 (Sun)</t>
+          <t>21/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4898,9 +4941,9 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4909,17 +4952,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>17/01/2026 (Sat)</t>
+          <t>18/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 3912</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 2694</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4928,7 +4971,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>14/01/2026 (Wed)</t>
+          <t>17/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4936,7 +4979,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4947,7 +4990,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11/01/2026 (Sun)</t>
+          <t>14/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4955,7 +4998,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4966,7 +5009,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10/01/2026 (Sat)</t>
+          <t>11/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4974,9 +5017,9 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4985,17 +5028,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/01/2026 (Wed)</t>
+          <t>10/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5263 4178 8612 6276 7308</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 3912</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5004,7 +5047,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>04/01/2026 (Sun)</t>
+          <t>07/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5012,7 +5055,7 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5023,7 +5066,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>03/01/2026 (Sat)</t>
+          <t>04/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5031,9 +5074,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5042,7 +5085,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31/12/2025 (Wed)</t>
+          <t>03/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5050,9 +5093,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5061,7 +5104,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>28/12/2025 (Sun)</t>
+          <t>31/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5069,9 +5112,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5080,15 +5123,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>27/12/2025 (Sat)</t>
+          <t>28/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5263 4178 6276 9746 7295</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
+          <t>5263 4178 8612 6276 7308</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5099,7 +5142,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>24/12/2025 (Wed)</t>
+          <t>27/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5107,7 +5150,7 @@
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5118,15 +5161,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>21/12/2025 (Sun)</t>
+          <t>24/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6276 7295 9746 6896 8391</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
+          <t>5263 4178 6276 9746 7295</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5137,7 +5180,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20/12/2025 (Sat)</t>
+          <t>21/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5145,7 +5188,7 @@
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5156,15 +5199,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>17/12/2025 (Wed)</t>
+          <t>20/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2056 2508</t>
-        </is>
-      </c>
-      <c r="C37" s="20" t="inlineStr">
+          <t>6276 7295 9746 6896 8391</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5175,17 +5218,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>14/12/2025 (Sun)</t>
+          <t>17/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2508 4748</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
+          <t>6276 7295 9746 2056 2508</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5194,7 +5237,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13/12/2025 (Sat)</t>
+          <t>14/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5202,9 +5245,9 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5213,7 +5256,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10/12/2025 (Wed)</t>
+          <t>13/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5221,7 +5264,7 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5232,15 +5275,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/12/2025 (Sun)</t>
+          <t>10/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6276 7295 9746 4748 7352</t>
-        </is>
-      </c>
-      <c r="C41" s="20" t="inlineStr">
+          <t>6276 7295 9746 2508 4748</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5251,15 +5294,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06/12/2025 (Sat)</t>
+          <t>07/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6276 7295 9746 7352 8590</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="inlineStr">
+          <t>6276 7295 9746 4748 7352</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5270,15 +5313,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>03/12/2025 (Wed)</t>
+          <t>06/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 4987</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
+          <t>6276 7295 9746 7352 8590</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5289,15 +5332,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>30/11/2025 (Sun)</t>
+          <t>03/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 1396</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="inlineStr">
+          <t>6276 7295 7352 8590 4987</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5308,15 +5351,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>29/11/2025 (Sat)</t>
+          <t>30/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6276 7295 8590 1396 9223</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
+          <t>6276 7295 7352 8590 1396</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5327,7 +5370,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26/11/2025 (Wed)</t>
+          <t>29/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5335,7 +5378,7 @@
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5346,15 +5389,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23/11/2025 (Sun)</t>
+          <t>26/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8590 1396 9223 3378 0316</t>
-        </is>
-      </c>
-      <c r="C47" s="16" t="inlineStr">
+          <t>6276 7295 8590 1396 9223</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5365,15 +5408,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22/11/2025 (Sat)</t>
+          <t>23/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1396 9223 0316 8612 7499</t>
-        </is>
-      </c>
-      <c r="C48" s="22" t="inlineStr">
+          <t>8590 1396 9223 3378 0316</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5384,7 +5427,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>19/11/2025 (Wed)</t>
+          <t>22/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5392,7 +5435,7 @@
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="C49" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5403,15 +5446,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16/11/2025 (Sun)</t>
+          <t>19/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>9223 0316 7499 8612 6456</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
+          <t>1396 9223 0316 8612 7499</t>
+        </is>
+      </c>
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5422,15 +5465,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15/11/2025 (Sat)</t>
+          <t>16/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9223 0316 8612 7499 6456</t>
-        </is>
-      </c>
-      <c r="C51" s="16" t="inlineStr">
+          <t>9223 0316 7499 8612 6456</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5441,15 +5484,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12/11/2025 (Wed)</t>
+          <t>15/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0316 8612 6456 7499 5548</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="inlineStr">
+          <t>9223 0316 8612 7499 6456</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5460,15 +5503,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09/11/2025 (Sun)</t>
+          <t>12/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0316 6456 8612 5548 0180</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
+          <t>0316 8612 6456 7499 5548</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5479,15 +5522,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08/11/2025 (Sat)</t>
+          <t>09/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0316 8612 5548 0180 8989</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
+          <t>0316 6456 8612 5548 0180</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5498,15 +5541,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>05/11/2025 (Wed)</t>
+          <t>08/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8989 4326</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="inlineStr">
+          <t>0316 8612 5548 0180 8989</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5517,17 +5560,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>02/11/2025 (Sun)</t>
+          <t>05/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0316 8612 5548 4326 8585</t>
-        </is>
-      </c>
-      <c r="C56" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
+          <t>0316 8612 5548 8989 4326</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5536,17 +5579,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01/11/2025 (Sat)</t>
+          <t>02/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3378 0316 8612 5548 8585</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>0316 8612 5548 4326 8585</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5555,15 +5598,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sun - 26/10/2025</t>
+          <t>01/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8585 4178</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="inlineStr">
+          <t>3378 0316 8612 5548 8585</t>
+        </is>
+      </c>
+      <c r="C58" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5574,17 +5617,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sat - 25/10/2025</t>
+          <t>Sun - 26/10/2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>8612 5548 8585 6143 8729</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+          <t>0316 8612 5548 8585 4178</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5593,15 +5636,34 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Sat - 25/10/2025</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>8612 5548 8585 6143 8729</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,10 +594,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14/03/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>8 4 3 7
+0 2 8 6
+4 5 9 0
+5 6 7 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -605,14 +620,21 @@
 5 6 7 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 7/226 (3.10%)
+▶ Direct: 7/4302 (0.16%)
+▶ Total Sets hit: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -620,7 +642,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -642,7 +664,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -664,7 +686,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -686,7 +708,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -708,7 +730,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -730,7 +752,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -752,7 +774,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -774,7 +796,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -796,7 +818,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -818,7 +840,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -840,7 +862,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -862,7 +884,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -884,7 +906,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -906,7 +928,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -928,7 +950,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -950,7 +972,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -972,7 +994,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -994,7 +1016,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1016,7 +1038,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1038,7 +1060,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1060,7 +1082,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1082,7 +1104,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1104,7 +1126,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1126,7 +1148,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1324,7 +1346,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1346,7 +1368,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1368,7 +1390,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1390,7 +1412,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1412,7 +1434,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1434,7 +1456,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1456,7 +1478,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1478,7 +1500,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1566,7 +1588,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1698,7 +1720,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1720,7 +1742,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1830,7 +1852,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1852,7 +1874,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1860,13 +1882,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1874,7 +1896,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1882,13 +1904,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1896,7 +1918,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1904,13 +1926,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1918,7 +1940,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1926,13 +1948,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1940,7 +1962,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1948,17 +1970,17 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="1" t="n"/>
-    </row>
     <row r="65">
-      <c r="B65" s="1" t="n"/>
+      <c r="B65" s="4" t="n"/>
       <c r="C65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="B66" s="1" t="n"/>
       <c r="C66" s="1" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="n"/>
+      <c r="C67" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1971,7 +1993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1999,10 +2021,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>11/03/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>1 9 3 3
+0 7 4 7
+2 4 2 0
+6 8 5 5</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 14/4212 (0.33%)
+✅ iBet: 14/223 (6.28%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -2010,20 +2053,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -2031,20 +2074,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -2052,20 +2095,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -2073,20 +2116,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -2094,20 +2137,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -2115,20 +2158,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -2136,20 +2179,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -2157,20 +2200,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2178,20 +2221,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2199,20 +2242,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2220,20 +2263,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2241,20 +2284,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2262,20 +2305,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2283,20 +2326,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2304,20 +2347,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2325,20 +2368,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2346,20 +2389,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2367,20 +2410,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2388,20 +2431,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2409,20 +2452,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2430,20 +2473,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2451,20 +2494,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2472,20 +2515,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2493,20 +2536,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2514,20 +2557,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2535,20 +2578,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2556,20 +2599,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2577,20 +2620,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2598,20 +2641,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2619,20 +2662,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2640,20 +2683,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2661,20 +2704,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2682,20 +2725,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2703,20 +2746,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2724,20 +2767,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2745,20 +2788,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2766,20 +2809,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2787,20 +2830,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2808,20 +2851,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2829,20 +2872,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2850,20 +2893,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2871,20 +2914,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2892,20 +2935,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2913,20 +2956,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2934,20 +2977,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2955,20 +2998,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -2976,20 +3019,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -2997,20 +3040,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -3018,20 +3061,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -3039,20 +3082,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -3060,20 +3103,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -3081,20 +3124,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -3102,20 +3145,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -3123,20 +3166,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -3144,20 +3187,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -3165,20 +3208,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3186,20 +3229,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3207,20 +3250,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3228,20 +3271,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3249,20 +3292,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3270,20 +3313,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3291,20 +3334,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3312,20 +3355,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3333,20 +3376,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3354,20 +3397,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3375,20 +3418,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3396,20 +3439,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3417,20 +3460,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3438,20 +3481,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3459,20 +3502,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3480,20 +3523,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3501,20 +3544,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3522,20 +3565,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3543,20 +3586,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3564,20 +3607,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3585,20 +3628,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3606,20 +3649,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3627,20 +3670,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3648,20 +3691,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3669,20 +3712,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3690,20 +3733,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3711,20 +3754,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3732,20 +3775,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3753,20 +3796,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3774,20 +3817,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3795,20 +3838,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3816,20 +3859,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3837,20 +3880,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3858,20 +3901,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3879,20 +3922,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3900,20 +3943,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3921,20 +3964,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3942,20 +3985,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -3963,20 +4006,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -3984,20 +4027,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -4005,20 +4048,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -4026,20 +4069,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -4047,20 +4090,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -4068,20 +4111,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -4089,20 +4132,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -4110,20 +4153,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -4131,20 +4174,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -4152,20 +4195,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4173,20 +4216,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4194,20 +4237,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4215,20 +4258,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4236,20 +4279,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4257,20 +4300,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4278,20 +4321,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4299,20 +4342,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4320,20 +4363,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4341,20 +4384,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4362,20 +4405,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4383,20 +4426,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4404,16 +4447,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="1" t="n"/>
-      <c r="C117" s="1" t="n"/>
     </row>
     <row r="118">
       <c r="B118" s="1" t="n"/>
@@ -4425,6 +4464,7 @@
     </row>
     <row r="120">
       <c r="B120" s="1" t="n"/>
+      <c r="C120" s="1" t="n"/>
     </row>
     <row r="121">
       <c r="B121" s="1" t="n"/>
@@ -4500,6 +4540,9 @@
     </row>
     <row r="145">
       <c r="B145" s="1" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4512,7 +4555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4540,20 +4583,20 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11/03/2026 (Wed)</t>
+          <t>14/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1516 7295 5263 4178 2645</t>
-        </is>
-      </c>
-      <c r="C2" s="19" t="inlineStr"/>
+          <t>1516 7295 5263 4178 3927</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/03/2026 (Sun)</t>
+          <t>11/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4561,9 +4604,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 1516 → 1651 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4572,7 +4615,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>08/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4580,7 +4623,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4591,7 +4634,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4599,7 +4642,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4610,7 +4653,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4618,7 +4661,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4629,7 +4672,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28/02/2026 (Sat)</t>
+          <t>01/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4637,9 +4680,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4648,17 +4691,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25/02/2026 (Wed)</t>
+          <t>28/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 6437</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4667,7 +4710,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22/02/2026 (Sun)</t>
+          <t>25/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4675,9 +4718,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4686,7 +4729,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21/02/2026 (Sat)</t>
+          <t>22/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4694,9 +4737,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4705,17 +4748,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/02/2026 (Wed)</t>
+          <t>21/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 7352</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
+          <t>7295 5263 4178 2645 6437</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4724,7 +4767,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15/02/2026 (Sun)</t>
+          <t>18/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4732,9 +4775,9 @@
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4743,15 +4786,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14/02/2026 (Sat)</t>
+          <t>15/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7295 5263 4178 7352 8612</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+          <t>7295 5263 4178 2645 7352</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4762,7 +4805,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11/02/2026 (Wed)</t>
+          <t>14/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4770,7 +4813,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4781,7 +4824,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/02/2026 (Sun)</t>
+          <t>11/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4789,7 +4832,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4800,7 +4843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/02/2026 (Sat)</t>
+          <t>08/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4808,7 +4851,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4819,7 +4862,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04/02/2026 (Wed)</t>
+          <t>07/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4827,7 +4870,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4838,7 +4881,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01/02/2026 (Sun)</t>
+          <t>04/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4846,7 +4889,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4857,7 +4900,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>31/01/2026 (Sat)</t>
+          <t>01/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4865,7 +4908,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4876,7 +4919,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28/01/2026 (Wed)</t>
+          <t>31/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4884,7 +4927,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4895,7 +4938,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25/01/2026 (Sun)</t>
+          <t>28/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4903,7 +4946,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4914,15 +4957,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24/01/2026 (Sat)</t>
+          <t>25/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 2694</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
+          <t>7295 5263 4178 7352 8612</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4933,7 +4976,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>21/01/2026 (Wed)</t>
+          <t>24/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4941,7 +4984,7 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4952,7 +4995,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>18/01/2026 (Sun)</t>
+          <t>21/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4960,9 +5003,9 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4971,17 +5014,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17/01/2026 (Sat)</t>
+          <t>18/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 3912</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 2694</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4990,7 +5033,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14/01/2026 (Wed)</t>
+          <t>17/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4998,7 +5041,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5009,7 +5052,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11/01/2026 (Sun)</t>
+          <t>14/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5017,7 +5060,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5028,7 +5071,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10/01/2026 (Sat)</t>
+          <t>11/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5036,9 +5079,9 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5047,17 +5090,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/01/2026 (Wed)</t>
+          <t>10/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5263 4178 8612 6276 7308</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 3912</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5066,7 +5109,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>04/01/2026 (Sun)</t>
+          <t>07/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5074,7 +5117,7 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5085,7 +5128,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>03/01/2026 (Sat)</t>
+          <t>04/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5093,9 +5136,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5104,7 +5147,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31/12/2025 (Wed)</t>
+          <t>03/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5112,9 +5155,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5123,7 +5166,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>28/12/2025 (Sun)</t>
+          <t>31/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5131,9 +5174,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5142,15 +5185,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>27/12/2025 (Sat)</t>
+          <t>28/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5263 4178 6276 9746 7295</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
+          <t>5263 4178 8612 6276 7308</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5161,7 +5204,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>24/12/2025 (Wed)</t>
+          <t>27/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5169,7 +5212,7 @@
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5180,15 +5223,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>21/12/2025 (Sun)</t>
+          <t>24/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6276 7295 9746 6896 8391</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
+          <t>5263 4178 6276 9746 7295</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5199,7 +5242,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20/12/2025 (Sat)</t>
+          <t>21/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5207,7 +5250,7 @@
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5218,15 +5261,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17/12/2025 (Wed)</t>
+          <t>20/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2056 2508</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
+          <t>6276 7295 9746 6896 8391</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5237,17 +5280,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>14/12/2025 (Sun)</t>
+          <t>17/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2508 4748</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
+          <t>6276 7295 9746 2056 2508</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5256,7 +5299,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13/12/2025 (Sat)</t>
+          <t>14/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5264,9 +5307,9 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5275,7 +5318,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10/12/2025 (Wed)</t>
+          <t>13/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5283,7 +5326,7 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5294,15 +5337,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/12/2025 (Sun)</t>
+          <t>10/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6276 7295 9746 4748 7352</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
+          <t>6276 7295 9746 2508 4748</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5313,15 +5356,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06/12/2025 (Sat)</t>
+          <t>07/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6276 7295 9746 7352 8590</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
+          <t>6276 7295 9746 4748 7352</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5332,15 +5375,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>03/12/2025 (Wed)</t>
+          <t>06/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 4987</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
+          <t>6276 7295 9746 7352 8590</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5351,15 +5394,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>30/11/2025 (Sun)</t>
+          <t>03/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 1396</t>
-        </is>
-      </c>
-      <c r="C45" s="22" t="inlineStr">
+          <t>6276 7295 7352 8590 4987</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5370,15 +5413,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>29/11/2025 (Sat)</t>
+          <t>30/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6276 7295 8590 1396 9223</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
+          <t>6276 7295 7352 8590 1396</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5389,7 +5432,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26/11/2025 (Wed)</t>
+          <t>29/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5397,7 +5440,7 @@
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5408,15 +5451,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23/11/2025 (Sun)</t>
+          <t>26/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8590 1396 9223 3378 0316</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
+          <t>6276 7295 8590 1396 9223</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5427,15 +5470,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22/11/2025 (Sat)</t>
+          <t>23/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1396 9223 0316 8612 7499</t>
-        </is>
-      </c>
-      <c r="C49" s="22" t="inlineStr">
+          <t>8590 1396 9223 3378 0316</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5446,7 +5489,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19/11/2025 (Wed)</t>
+          <t>22/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5454,7 +5497,7 @@
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="C50" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5465,15 +5508,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16/11/2025 (Sun)</t>
+          <t>19/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9223 0316 7499 8612 6456</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
+          <t>1396 9223 0316 8612 7499</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5484,15 +5527,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>15/11/2025 (Sat)</t>
+          <t>16/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9223 0316 8612 7499 6456</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
+          <t>9223 0316 7499 8612 6456</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5503,15 +5546,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>12/11/2025 (Wed)</t>
+          <t>15/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0316 8612 6456 7499 5548</t>
-        </is>
-      </c>
-      <c r="C53" s="22" t="inlineStr">
+          <t>9223 0316 8612 7499 6456</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5522,15 +5565,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09/11/2025 (Sun)</t>
+          <t>12/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0316 6456 8612 5548 0180</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr">
+          <t>0316 8612 6456 7499 5548</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5541,15 +5584,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08/11/2025 (Sat)</t>
+          <t>09/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0316 8612 5548 0180 8989</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
+          <t>0316 6456 8612 5548 0180</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5560,15 +5603,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05/11/2025 (Wed)</t>
+          <t>08/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8989 4326</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="inlineStr">
+          <t>0316 8612 5548 0180 8989</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5579,17 +5622,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>02/11/2025 (Sun)</t>
+          <t>05/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0316 8612 5548 4326 8585</t>
-        </is>
-      </c>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
+          <t>0316 8612 5548 8989 4326</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5598,17 +5641,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01/11/2025 (Sat)</t>
+          <t>02/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3378 0316 8612 5548 8585</t>
-        </is>
-      </c>
-      <c r="C58" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>0316 8612 5548 4326 8585</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5617,15 +5660,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sun - 26/10/2025</t>
+          <t>01/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8585 4178</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
+          <t>3378 0316 8612 5548 8585</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5636,17 +5679,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sat - 25/10/2025</t>
+          <t>Sun - 26/10/2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>8612 5548 8585 6143 8729</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+          <t>0316 8612 5548 8585 4178</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5655,15 +5698,34 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Sat - 25/10/2025</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>8612 5548 8585 6143 8729</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C62" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,10 +594,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>8 4 3 7
+0 2 1 6
+4 5 9 8
+5 6 7 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -605,14 +620,21 @@
 5 6 7 1</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 13/226 (5.75%)
+▶ Direct: 13/4302 (0.30%)
+▶ Total Sets hit: 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -620,7 +642,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -642,7 +664,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -664,7 +686,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -686,7 +708,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -708,7 +730,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -730,7 +752,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -752,7 +774,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -774,7 +796,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -796,7 +818,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -818,7 +840,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -840,7 +862,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -862,7 +884,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -884,7 +906,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -906,7 +928,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -928,7 +950,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -950,7 +972,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -972,7 +994,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -994,7 +1016,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1016,7 +1038,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1038,7 +1060,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1060,7 +1082,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1082,7 +1104,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1104,7 +1126,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1126,7 +1148,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1148,7 +1170,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1324,7 +1346,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1346,7 +1368,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1368,7 +1390,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1390,7 +1412,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1412,7 +1434,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1434,7 +1456,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1456,7 +1478,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1500,7 +1522,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1522,7 +1544,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1588,7 +1610,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1610,7 +1632,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1698,7 +1720,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1720,7 +1742,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1742,7 +1764,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1830,7 +1852,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1852,7 +1874,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1860,13 +1882,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1874,7 +1896,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1882,13 +1904,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1896,7 +1918,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1904,13 +1926,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1918,7 +1940,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1926,13 +1948,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1940,7 +1962,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1948,13 +1970,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1962,7 +1984,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1970,17 +1992,17 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="1" t="n"/>
-    </row>
     <row r="66">
-      <c r="B66" s="1" t="n"/>
+      <c r="B66" s="4" t="n"/>
       <c r="C66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="1" t="n"/>
       <c r="C67" s="1" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="n"/>
+      <c r="C68" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1993,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2021,10 +2043,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>14/03/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>4 4 0 3
+9 8 1 1
+5 6 6 0
+7 3 9 2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 14/4302 (0.33%)
+✅ iBet: 14/226 (6.19%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -2032,20 +2075,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -2053,20 +2096,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -2074,20 +2117,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -2095,20 +2138,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -2116,20 +2159,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -2137,20 +2180,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -2158,20 +2201,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -2179,20 +2222,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -2200,20 +2243,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2221,20 +2264,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2242,20 +2285,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2263,20 +2306,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2284,20 +2327,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2305,20 +2348,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2326,20 +2369,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2347,20 +2390,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2368,20 +2411,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2389,20 +2432,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2410,20 +2453,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2431,20 +2474,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2452,20 +2495,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2473,20 +2516,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2494,20 +2537,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2515,20 +2558,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2536,20 +2579,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2557,20 +2600,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2578,20 +2621,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2599,20 +2642,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2620,20 +2663,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2641,20 +2684,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2662,20 +2705,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2683,20 +2726,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2704,20 +2747,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2725,20 +2768,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2746,20 +2789,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2767,20 +2810,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2788,20 +2831,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2809,20 +2852,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2830,20 +2873,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2851,20 +2894,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2872,20 +2915,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2893,20 +2936,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2914,20 +2957,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2935,20 +2978,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2956,20 +2999,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -2977,20 +3020,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -2998,20 +3041,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -3019,20 +3062,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -3040,20 +3083,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -3061,20 +3104,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -3082,20 +3125,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -3103,20 +3146,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -3124,20 +3167,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -3145,20 +3188,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -3166,20 +3209,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -3187,20 +3230,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -3208,20 +3251,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3229,20 +3272,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3250,20 +3293,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3271,20 +3314,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3292,20 +3335,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3313,20 +3356,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3334,20 +3377,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3355,20 +3398,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3376,20 +3419,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3397,20 +3440,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3418,20 +3461,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3439,20 +3482,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3460,20 +3503,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3481,20 +3524,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3502,20 +3545,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3523,20 +3566,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3544,20 +3587,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3565,20 +3608,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3586,20 +3629,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3607,20 +3650,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3628,20 +3671,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3649,20 +3692,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3670,20 +3713,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3691,20 +3734,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3712,20 +3755,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3733,20 +3776,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3754,20 +3797,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3775,20 +3818,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3796,20 +3839,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3817,20 +3860,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3838,20 +3881,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3859,20 +3902,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3880,20 +3923,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3901,20 +3944,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3922,20 +3965,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3943,20 +3986,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -3964,20 +4007,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -3985,20 +4028,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -4006,20 +4049,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -4027,20 +4070,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -4048,20 +4091,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -4069,20 +4112,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -4090,20 +4133,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -4111,20 +4154,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -4132,20 +4175,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -4153,20 +4196,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -4174,20 +4217,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -4195,20 +4238,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4216,20 +4259,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4237,20 +4280,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4258,20 +4301,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4279,20 +4322,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4300,20 +4343,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4321,20 +4364,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4342,20 +4385,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4363,20 +4406,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4384,20 +4427,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4405,20 +4448,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4426,20 +4469,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4447,16 +4490,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="1" t="n"/>
-      <c r="C118" s="1" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="1" t="n"/>
@@ -4468,6 +4507,7 @@
     </row>
     <row r="121">
       <c r="B121" s="1" t="n"/>
+      <c r="C121" s="1" t="n"/>
     </row>
     <row r="122">
       <c r="B122" s="1" t="n"/>
@@ -4543,6 +4583,9 @@
     </row>
     <row r="146">
       <c r="B146" s="1" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4555,7 +4598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4583,7 +4626,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14/03/2026 (Sat)</t>
+          <t>15/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4591,22 +4634,22 @@
           <t>1516 7295 5263 4178 3927</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr"/>
+      <c r="C2" s="23" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/03/2026 (Wed)</t>
+          <t>14/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1516 7295 5263 4178 2645</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 1516 → 1651 (Starter)
+          <t>1516 7295 5263 4178 3927</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4615,7 +4658,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/03/2026 (Sun)</t>
+          <t>11/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4623,9 +4666,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 1516 → 1651 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4634,7 +4677,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>08/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4642,7 +4685,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4653,7 +4696,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4661,7 +4704,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4672,7 +4715,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4680,7 +4723,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4691,7 +4734,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28/02/2026 (Sat)</t>
+          <t>01/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4699,9 +4742,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4710,17 +4753,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25/02/2026 (Wed)</t>
+          <t>28/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 6437</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4729,7 +4772,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22/02/2026 (Sun)</t>
+          <t>25/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4737,9 +4780,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4748,7 +4791,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21/02/2026 (Sat)</t>
+          <t>22/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4756,9 +4799,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4767,17 +4810,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18/02/2026 (Wed)</t>
+          <t>21/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 7352</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
+          <t>7295 5263 4178 2645 6437</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4786,7 +4829,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15/02/2026 (Sun)</t>
+          <t>18/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4794,9 +4837,9 @@
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4805,15 +4848,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14/02/2026 (Sat)</t>
+          <t>15/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7295 5263 4178 7352 8612</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+          <t>7295 5263 4178 2645 7352</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4824,7 +4867,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11/02/2026 (Wed)</t>
+          <t>14/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4832,7 +4875,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4843,7 +4886,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/02/2026 (Sun)</t>
+          <t>11/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4851,7 +4894,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4862,7 +4905,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/02/2026 (Sat)</t>
+          <t>08/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4870,7 +4913,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4881,7 +4924,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04/02/2026 (Wed)</t>
+          <t>07/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4889,7 +4932,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4900,7 +4943,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01/02/2026 (Sun)</t>
+          <t>04/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4908,7 +4951,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4919,7 +4962,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31/01/2026 (Sat)</t>
+          <t>01/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4927,7 +4970,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4938,7 +4981,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28/01/2026 (Wed)</t>
+          <t>31/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4946,7 +4989,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4957,7 +5000,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25/01/2026 (Sun)</t>
+          <t>28/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4965,7 +5008,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4976,15 +5019,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24/01/2026 (Sat)</t>
+          <t>25/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 2694</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
+          <t>7295 5263 4178 7352 8612</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4995,7 +5038,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>21/01/2026 (Wed)</t>
+          <t>24/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5003,7 +5046,7 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5014,7 +5057,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>18/01/2026 (Sun)</t>
+          <t>21/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5022,9 +5065,9 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5033,17 +5076,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>17/01/2026 (Sat)</t>
+          <t>18/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 3912</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 2694</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5052,7 +5095,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>14/01/2026 (Wed)</t>
+          <t>17/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5060,7 +5103,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5071,7 +5114,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>11/01/2026 (Sun)</t>
+          <t>14/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5079,7 +5122,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5090,7 +5133,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10/01/2026 (Sat)</t>
+          <t>11/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5098,9 +5141,9 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5109,17 +5152,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/01/2026 (Wed)</t>
+          <t>10/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5263 4178 8612 6276 7308</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 3912</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5128,7 +5171,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>04/01/2026 (Sun)</t>
+          <t>07/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5136,7 +5179,7 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5147,7 +5190,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>03/01/2026 (Sat)</t>
+          <t>04/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5155,9 +5198,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5166,7 +5209,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31/12/2025 (Wed)</t>
+          <t>03/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5174,9 +5217,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5185,7 +5228,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28/12/2025 (Sun)</t>
+          <t>31/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5193,9 +5236,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5204,15 +5247,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>27/12/2025 (Sat)</t>
+          <t>28/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5263 4178 6276 9746 7295</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
+          <t>5263 4178 8612 6276 7308</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5223,7 +5266,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>24/12/2025 (Wed)</t>
+          <t>27/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5231,7 +5274,7 @@
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5242,15 +5285,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>21/12/2025 (Sun)</t>
+          <t>24/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6276 7295 9746 6896 8391</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
+          <t>5263 4178 6276 9746 7295</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5261,7 +5304,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20/12/2025 (Sat)</t>
+          <t>21/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5269,7 +5312,7 @@
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C38" s="22" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5280,15 +5323,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17/12/2025 (Wed)</t>
+          <t>20/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2056 2508</t>
-        </is>
-      </c>
-      <c r="C39" s="20" t="inlineStr">
+          <t>6276 7295 9746 6896 8391</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5299,17 +5342,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14/12/2025 (Sun)</t>
+          <t>17/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2508 4748</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
+          <t>6276 7295 9746 2056 2508</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5318,7 +5361,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13/12/2025 (Sat)</t>
+          <t>14/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5326,9 +5369,9 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5337,7 +5380,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10/12/2025 (Wed)</t>
+          <t>13/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5345,7 +5388,7 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5356,15 +5399,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/12/2025 (Sun)</t>
+          <t>10/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6276 7295 9746 4748 7352</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
+          <t>6276 7295 9746 2508 4748</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5375,15 +5418,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/12/2025 (Sat)</t>
+          <t>07/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6276 7295 9746 7352 8590</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
+          <t>6276 7295 9746 4748 7352</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5394,15 +5437,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>03/12/2025 (Wed)</t>
+          <t>06/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 4987</t>
-        </is>
-      </c>
-      <c r="C45" s="16" t="inlineStr">
+          <t>6276 7295 9746 7352 8590</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5413,15 +5456,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>30/11/2025 (Sun)</t>
+          <t>03/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 1396</t>
-        </is>
-      </c>
-      <c r="C46" s="22" t="inlineStr">
+          <t>6276 7295 7352 8590 4987</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5432,15 +5475,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>29/11/2025 (Sat)</t>
+          <t>30/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6276 7295 8590 1396 9223</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
+          <t>6276 7295 7352 8590 1396</t>
+        </is>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5451,7 +5494,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26/11/2025 (Wed)</t>
+          <t>29/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5459,7 +5502,7 @@
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5470,15 +5513,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>23/11/2025 (Sun)</t>
+          <t>26/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>8590 1396 9223 3378 0316</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr">
+          <t>6276 7295 8590 1396 9223</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5489,15 +5532,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22/11/2025 (Sat)</t>
+          <t>23/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1396 9223 0316 8612 7499</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="inlineStr">
+          <t>8590 1396 9223 3378 0316</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5508,7 +5551,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19/11/2025 (Wed)</t>
+          <t>22/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5516,7 +5559,7 @@
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C51" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5527,15 +5570,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16/11/2025 (Sun)</t>
+          <t>19/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>9223 0316 7499 8612 6456</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
+          <t>1396 9223 0316 8612 7499</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5546,15 +5589,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>15/11/2025 (Sat)</t>
+          <t>16/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9223 0316 8612 7499 6456</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="inlineStr">
+          <t>9223 0316 7499 8612 6456</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5565,15 +5608,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>12/11/2025 (Wed)</t>
+          <t>15/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0316 8612 6456 7499 5548</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="inlineStr">
+          <t>9223 0316 8612 7499 6456</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5584,15 +5627,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09/11/2025 (Sun)</t>
+          <t>12/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0316 6456 8612 5548 0180</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
+          <t>0316 8612 6456 7499 5548</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5603,15 +5646,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08/11/2025 (Sat)</t>
+          <t>09/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0316 8612 5548 0180 8989</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
+          <t>0316 6456 8612 5548 0180</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5622,15 +5665,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05/11/2025 (Wed)</t>
+          <t>08/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8989 4326</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
+          <t>0316 8612 5548 0180 8989</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5641,17 +5684,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>02/11/2025 (Sun)</t>
+          <t>05/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0316 8612 5548 4326 8585</t>
-        </is>
-      </c>
-      <c r="C58" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
+          <t>0316 8612 5548 8989 4326</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5660,17 +5703,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01/11/2025 (Sat)</t>
+          <t>02/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3378 0316 8612 5548 8585</t>
-        </is>
-      </c>
-      <c r="C59" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>0316 8612 5548 4326 8585</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5679,15 +5722,15 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sun - 26/10/2025</t>
+          <t>01/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8585 4178</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="inlineStr">
+          <t>3378 0316 8612 5548 8585</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5698,17 +5741,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sat - 25/10/2025</t>
+          <t>Sun - 26/10/2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8612 5548 8585 6143 8729</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+          <t>0316 8612 5548 8585 4178</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5717,15 +5760,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>Sat - 25/10/2025</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>8612 5548 8585 6143 8729</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -594,7 +594,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/03/2026 (Sun)</t>
+          <t>18/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
@@ -609,10 +609,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>15/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>8 4 3 7
+0 2 1 6
+4 5 9 8
+5 6 7 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 7/208 (3.37%)
+▶ Direct: 7/3864 (0.18%)
+▶ Total Sets hit: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -620,7 +642,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -628,13 +650,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -642,7 +664,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -650,13 +672,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -664,7 +686,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -672,13 +694,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -686,7 +708,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -694,13 +716,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -708,7 +730,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -716,13 +738,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -730,7 +752,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -738,13 +760,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -752,7 +774,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -760,13 +782,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -774,7 +796,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -782,13 +804,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -796,7 +818,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -804,13 +826,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -818,7 +840,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -826,13 +848,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -840,7 +862,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -848,13 +870,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -862,7 +884,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -870,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -884,7 +906,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -892,13 +914,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -906,7 +928,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -914,13 +936,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -928,7 +950,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -936,13 +958,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -950,7 +972,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -958,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -972,7 +994,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -980,13 +1002,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -994,7 +1016,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -1002,13 +1024,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -1016,7 +1038,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1024,13 +1046,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1038,7 +1060,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1046,13 +1068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1060,7 +1082,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1068,13 +1090,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1082,7 +1104,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1090,13 +1112,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1104,7 +1126,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1112,13 +1134,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1126,7 +1148,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1134,13 +1156,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1148,7 +1170,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1156,13 +1178,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1170,7 +1192,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1178,13 +1200,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1192,7 +1214,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1200,13 +1222,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1214,7 +1236,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1222,13 +1244,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1236,7 +1258,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1244,13 +1266,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1258,7 +1280,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1266,13 +1288,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1280,7 +1302,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1288,13 +1310,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1302,7 +1324,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1310,13 +1332,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1324,7 +1346,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1332,13 +1354,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1346,7 +1368,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1354,13 +1376,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1368,7 +1390,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1376,13 +1398,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1390,7 +1412,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1398,13 +1420,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1412,7 +1434,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1420,13 +1442,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1434,7 +1456,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1442,13 +1464,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1456,7 +1478,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1464,13 +1486,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1478,7 +1500,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1486,13 +1508,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1500,7 +1522,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1508,13 +1530,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1522,7 +1544,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1530,13 +1552,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1544,7 +1566,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1552,13 +1574,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1566,7 +1588,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1574,13 +1596,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1588,7 +1610,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1596,13 +1618,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1610,7 +1632,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1618,13 +1640,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1632,7 +1654,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1640,13 +1662,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1654,7 +1676,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1662,13 +1684,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -1676,7 +1698,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -1684,13 +1706,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1698,7 +1720,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1706,13 +1728,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -1720,7 +1742,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1728,13 +1750,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -1742,7 +1764,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1750,13 +1772,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1764,7 +1786,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1772,13 +1794,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="15" t="inlineStr">
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -1786,7 +1808,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1794,13 +1816,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -1808,7 +1830,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1816,13 +1838,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1830,7 +1852,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1838,13 +1860,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1852,7 +1874,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -1860,13 +1882,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1874,7 +1896,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1882,13 +1904,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -1896,7 +1918,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1904,13 +1926,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1918,7 +1940,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1926,13 +1948,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -1940,7 +1962,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1948,13 +1970,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -1962,7 +1984,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1970,13 +1992,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -1984,7 +2006,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -1992,17 +2014,17 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="1" t="n"/>
-    </row>
     <row r="67">
-      <c r="B67" s="1" t="n"/>
+      <c r="B67" s="4" t="n"/>
       <c r="C67" s="1" t="n"/>
     </row>
     <row r="68">
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="1" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="n"/>
+      <c r="C69" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2015,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2043,10 +2065,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>15/03/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>8 4 4 1
+6 6 9 7
+0 0 1 2
+3 8 7 5</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 12/3672 (0.33%)
+✅ iBet: 12/195 (6.15%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -2054,20 +2097,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -2075,20 +2118,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -2096,20 +2139,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -2117,20 +2160,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -2138,20 +2181,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -2159,20 +2202,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -2180,20 +2223,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -2201,20 +2244,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -2222,20 +2265,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -2243,20 +2286,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -2264,20 +2307,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -2285,20 +2328,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -2306,20 +2349,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -2327,20 +2370,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -2348,20 +2391,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -2369,20 +2412,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -2390,20 +2433,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -2411,20 +2454,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -2432,20 +2475,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -2453,20 +2496,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -2474,20 +2517,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -2495,20 +2538,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -2516,20 +2559,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -2537,20 +2580,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -2558,20 +2601,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -2579,20 +2622,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -2600,20 +2643,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -2621,20 +2664,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -2642,20 +2685,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -2663,20 +2706,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -2684,20 +2727,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -2705,20 +2748,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -2726,20 +2769,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -2747,20 +2790,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -2768,20 +2811,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -2789,20 +2832,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -2810,20 +2853,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -2831,20 +2874,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -2852,20 +2895,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -2873,20 +2916,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -2894,20 +2937,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -2915,20 +2958,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -2936,20 +2979,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -2957,20 +3000,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -2978,20 +3021,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -2999,20 +3042,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -3020,20 +3063,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -3041,20 +3084,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -3062,20 +3105,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="14" t="inlineStr">
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -3083,20 +3126,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="14" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -3104,20 +3147,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -3125,20 +3168,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="14" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -3146,20 +3189,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -3167,20 +3210,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -3188,20 +3231,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -3209,20 +3252,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -3230,20 +3273,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -3251,20 +3294,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -3272,20 +3315,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -3293,20 +3336,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -3314,20 +3357,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -3335,20 +3378,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -3356,20 +3399,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -3377,20 +3420,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -3398,20 +3441,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -3419,20 +3462,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -3440,20 +3483,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -3461,20 +3504,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -3482,20 +3525,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -3503,20 +3546,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -3524,20 +3567,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -3545,20 +3588,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -3566,20 +3609,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -3587,20 +3630,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -3608,20 +3651,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -3629,20 +3672,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -3650,20 +3693,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -3671,20 +3714,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -3692,20 +3735,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -3713,20 +3756,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -3734,20 +3777,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -3755,20 +3798,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -3776,20 +3819,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -3797,20 +3840,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -3818,20 +3861,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -3839,20 +3882,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -3860,20 +3903,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -3881,20 +3924,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -3902,20 +3945,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -3923,20 +3966,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -3944,20 +3987,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -3965,20 +4008,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -3986,20 +4029,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -4007,20 +4050,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -4028,20 +4071,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -4049,20 +4092,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -4070,20 +4113,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -4091,20 +4134,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -4112,20 +4155,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -4133,20 +4176,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -4154,20 +4197,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -4175,20 +4218,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -4196,20 +4239,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -4217,20 +4260,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -4238,20 +4281,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -4259,20 +4302,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -4280,20 +4323,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -4301,20 +4344,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -4322,20 +4365,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -4343,20 +4386,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -4364,20 +4407,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -4385,20 +4428,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -4406,20 +4449,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -4427,20 +4470,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -4448,20 +4491,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -4469,20 +4512,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -4490,16 +4533,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="1" t="n"/>
-      <c r="C119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="B120" s="1" t="n"/>
@@ -4511,6 +4550,7 @@
     </row>
     <row r="122">
       <c r="B122" s="1" t="n"/>
+      <c r="C122" s="1" t="n"/>
     </row>
     <row r="123">
       <c r="B123" s="1" t="n"/>
@@ -4586,6 +4626,9 @@
     </row>
     <row r="147">
       <c r="B147" s="1" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4598,7 +4641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4626,7 +4669,7 @@
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15/03/2026 (Sun)</t>
+          <t>18/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4634,12 +4677,12 @@
           <t>1516 7295 5263 4178 3927</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr"/>
+      <c r="C2" s="17" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14/03/2026 (Sat)</t>
+          <t>15/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4647,7 +4690,7 @@
           <t>1516 7295 5263 4178 3927</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4658,17 +4701,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11/03/2026 (Wed)</t>
+          <t>14/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1516 7295 5263 4178 2645</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 1516 → 1651 (Starter)
+          <t>1516 7295 5263 4178 3927</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4677,7 +4720,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/03/2026 (Sun)</t>
+          <t>11/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4685,9 +4728,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 1516 → 1651 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4696,7 +4739,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/03/2026 (Sat)</t>
+          <t>08/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4704,7 +4747,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4715,7 +4758,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04/03/2026 (Wed)</t>
+          <t>07/03/2026 (Sat)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4723,7 +4766,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4734,7 +4777,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01/03/2026 (Sun)</t>
+          <t>04/03/2026 (Wed)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4742,7 +4785,7 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4753,7 +4796,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28/02/2026 (Sat)</t>
+          <t>01/03/2026 (Sun)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4761,9 +4804,9 @@
           <t>1516 7295 5263 4178 2645</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4772,17 +4815,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25/02/2026 (Wed)</t>
+          <t>28/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 6437</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
+          <t>1516 7295 5263 4178 2645</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 2645 → 4256 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4791,7 +4834,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22/02/2026 (Sun)</t>
+          <t>25/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4799,9 +4842,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 6437 → 6473 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4810,7 +4853,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21/02/2026 (Sat)</t>
+          <t>22/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4818,9 +4861,9 @@
           <t>7295 5263 4178 2645 6437</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4829,17 +4872,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18/02/2026 (Wed)</t>
+          <t>21/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7295 5263 4178 2645 7352</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
+          <t>7295 5263 4178 2645 6437</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8174 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4848,7 +4891,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15/02/2026 (Sun)</t>
+          <t>18/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4856,9 +4899,9 @@
           <t>7295 5263 4178 2645 7352</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5273 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -4867,15 +4910,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14/02/2026 (Sat)</t>
+          <t>15/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7295 5263 4178 7352 8612</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+          <t>7295 5263 4178 2645 7352</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4886,7 +4929,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11/02/2026 (Wed)</t>
+          <t>14/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4894,7 +4937,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4905,7 +4948,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/02/2026 (Sun)</t>
+          <t>11/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4913,7 +4956,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4924,7 +4967,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/02/2026 (Sat)</t>
+          <t>08/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4932,7 +4975,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4943,7 +4986,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04/02/2026 (Wed)</t>
+          <t>07/02/2026 (Sat)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4951,7 +4994,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4962,7 +5005,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01/02/2026 (Sun)</t>
+          <t>04/02/2026 (Wed)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4970,7 +5013,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -4981,7 +5024,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31/01/2026 (Sat)</t>
+          <t>01/02/2026 (Sun)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4989,7 +5032,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5000,7 +5043,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28/01/2026 (Wed)</t>
+          <t>31/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5008,7 +5051,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C22" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5019,7 +5062,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>25/01/2026 (Sun)</t>
+          <t>28/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5027,7 +5070,7 @@
           <t>7295 5263 4178 7352 8612</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5038,15 +5081,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>24/01/2026 (Sat)</t>
+          <t>25/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 2694</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
+          <t>7295 5263 4178 7352 8612</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5057,7 +5100,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>21/01/2026 (Wed)</t>
+          <t>24/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5065,7 +5108,7 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5076,7 +5119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>18/01/2026 (Sun)</t>
+          <t>21/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5084,9 +5127,9 @@
           <t>5263 4178 7352 8612 2694</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5095,17 +5138,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>17/01/2026 (Sat)</t>
+          <t>18/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5263 4178 7352 8612 3912</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 2694</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 3527 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5114,7 +5157,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14/01/2026 (Wed)</t>
+          <t>17/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5122,7 +5165,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5133,7 +5176,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11/01/2026 (Sun)</t>
+          <t>14/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5141,7 +5184,7 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5152,7 +5195,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10/01/2026 (Sat)</t>
+          <t>11/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5160,9 +5203,9 @@
           <t>5263 4178 7352 8612 3912</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5171,17 +5214,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/01/2026 (Wed)</t>
+          <t>10/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5263 4178 8612 6276 7308</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>5263 4178 7352 8612 3912</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7352 → 5327 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5190,7 +5233,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>04/01/2026 (Sun)</t>
+          <t>07/01/2026 (Wed)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5198,7 +5241,7 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5209,7 +5252,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>03/01/2026 (Sat)</t>
+          <t>04/01/2026 (Sun)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5217,9 +5260,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5228,7 +5271,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>31/12/2025 (Wed)</t>
+          <t>03/01/2026 (Sat)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5236,9 +5279,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 4178 → 8741 (Starter)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5247,7 +5290,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28/12/2025 (Sun)</t>
+          <t>31/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5255,9 +5298,9 @@
           <t>5263 4178 8612 6276 7308</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 2/5 (40.00%) - 4178 → 4781 (Consolation), 6276 → 2766 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5266,15 +5309,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27/12/2025 (Sat)</t>
+          <t>28/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5263 4178 6276 9746 7295</t>
-        </is>
-      </c>
-      <c r="C36" s="20" t="inlineStr">
+          <t>5263 4178 8612 6276 7308</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5285,7 +5328,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>24/12/2025 (Wed)</t>
+          <t>27/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5293,7 +5336,7 @@
           <t>5263 4178 6276 9746 7295</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5304,15 +5347,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>21/12/2025 (Sun)</t>
+          <t>24/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6276 7295 9746 6896 8391</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
+          <t>5263 4178 6276 9746 7295</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5323,7 +5366,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20/12/2025 (Sat)</t>
+          <t>21/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5331,7 +5374,7 @@
           <t>6276 7295 9746 6896 8391</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5342,15 +5385,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17/12/2025 (Wed)</t>
+          <t>20/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2056 2508</t>
-        </is>
-      </c>
-      <c r="C40" s="20" t="inlineStr">
+          <t>6276 7295 9746 6896 8391</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5361,17 +5404,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14/12/2025 (Sun)</t>
+          <t>17/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6276 7295 9746 2508 4748</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
+          <t>6276 7295 9746 2056 2508</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5380,7 +5423,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13/12/2025 (Sat)</t>
+          <t>14/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5388,9 +5431,9 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 7295 → 7259 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5399,7 +5442,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/12/2025 (Wed)</t>
+          <t>13/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5407,7 +5450,7 @@
           <t>6276 7295 9746 2508 4748</t>
         </is>
       </c>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5418,15 +5461,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/12/2025 (Sun)</t>
+          <t>10/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6276 7295 9746 4748 7352</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
+          <t>6276 7295 9746 2508 4748</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5437,15 +5480,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06/12/2025 (Sat)</t>
+          <t>07/12/2025 (Sun)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6276 7295 9746 7352 8590</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="inlineStr">
+          <t>6276 7295 9746 4748 7352</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5456,15 +5499,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>03/12/2025 (Wed)</t>
+          <t>06/12/2025 (Sat)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 4987</t>
-        </is>
-      </c>
-      <c r="C46" s="16" t="inlineStr">
+          <t>6276 7295 9746 7352 8590</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5475,15 +5518,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>30/11/2025 (Sun)</t>
+          <t>03/12/2025 (Wed)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6276 7295 7352 8590 1396</t>
-        </is>
-      </c>
-      <c r="C47" s="22" t="inlineStr">
+          <t>6276 7295 7352 8590 4987</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5494,15 +5537,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29/11/2025 (Sat)</t>
+          <t>30/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6276 7295 8590 1396 9223</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
+          <t>6276 7295 7352 8590 1396</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5513,7 +5556,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26/11/2025 (Wed)</t>
+          <t>29/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5521,7 +5564,7 @@
           <t>6276 7295 8590 1396 9223</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5532,15 +5575,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23/11/2025 (Sun)</t>
+          <t>26/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>8590 1396 9223 3378 0316</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
+          <t>6276 7295 8590 1396 9223</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5551,15 +5594,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22/11/2025 (Sat)</t>
+          <t>23/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1396 9223 0316 8612 7499</t>
-        </is>
-      </c>
-      <c r="C51" s="22" t="inlineStr">
+          <t>8590 1396 9223 3378 0316</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5570,7 +5613,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>19/11/2025 (Wed)</t>
+          <t>22/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5578,7 +5621,7 @@
           <t>1396 9223 0316 8612 7499</t>
         </is>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5589,15 +5632,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16/11/2025 (Sun)</t>
+          <t>19/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>9223 0316 7499 8612 6456</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
+          <t>1396 9223 0316 8612 7499</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5608,15 +5651,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15/11/2025 (Sat)</t>
+          <t>16/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9223 0316 8612 7499 6456</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
+          <t>9223 0316 7499 8612 6456</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5627,15 +5670,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>12/11/2025 (Wed)</t>
+          <t>15/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0316 8612 6456 7499 5548</t>
-        </is>
-      </c>
-      <c r="C55" s="22" t="inlineStr">
+          <t>9223 0316 8612 7499 6456</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5646,15 +5689,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09/11/2025 (Sun)</t>
+          <t>12/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0316 6456 8612 5548 0180</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
+          <t>0316 8612 6456 7499 5548</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5665,15 +5708,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08/11/2025 (Sat)</t>
+          <t>09/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0316 8612 5548 0180 8989</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
+          <t>0316 6456 8612 5548 0180</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5684,15 +5727,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>05/11/2025 (Wed)</t>
+          <t>08/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8989 4326</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
+          <t>0316 8612 5548 0180 8989</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5703,17 +5746,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>02/11/2025 (Sun)</t>
+          <t>05/11/2025 (Wed)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0316 8612 5548 4326 8585</t>
-        </is>
-      </c>
-      <c r="C59" s="22" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
+          <t>0316 8612 5548 8989 4326</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5722,17 +5765,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01/11/2025 (Sat)</t>
+          <t>02/11/2025 (Sun)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3378 0316 8612 5548 8585</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>▶ iBet: 0/5 (0.00%) - 
+          <t>0316 8612 5548 4326 8585</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8612 → 8621 (Consolation)
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5741,15 +5784,15 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sun - 26/10/2025</t>
+          <t>01/11/2025 (Sat)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0316 8612 5548 8585 4178</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
+          <t>3378 0316 8612 5548 8585</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
         <is>
           <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
@@ -5760,17 +5803,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sat - 25/10/2025</t>
+          <t>Sun - 26/10/2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>8612 5548 8585 6143 8729</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+          <t>0316 8612 5548 8585 4178</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>▶ iBet: 0/5 (0.00%) - 
 ▶ Direct: 0/5 (0.00%) - 
 ▶ Total Sets hit: 0</t>
         </is>
@@ -5779,15 +5822,34 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Sat - 25/10/2025</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>8612 5548 8585 6143 8729</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>▶ iBet: 1/5 (20.00%) - 8729 → 7829 (Consolation)
+▶ Direct: 0/5 (0.00%) - 
+▶ Total Sets hit: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Wed - 22/10/2025</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>8612 6143 2503 6532 1438</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C64" s="10" t="inlineStr">
         <is>
           <t>▶ iBet: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)
 ▶ Direct: 5/5 (100.00%) - 8612 (1st), 6143 (2nd), 2503 (3rd), 6532 (Starter), 1438 (Starter)

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,10 +527,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03/05/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>3 4 1 7
+0 2 8 6
+2 5 9 4
+5 1 7 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -538,14 +553,21 @@
 5 6 9 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 8/226 (3.54%)
+▶ Direct: 8/4302 (0.19%)
+▶ Total Sets hit: 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -553,7 +575,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -561,13 +583,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -575,7 +597,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -583,13 +605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -597,7 +619,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -605,13 +627,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -619,7 +641,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -627,13 +649,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -641,7 +663,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -649,13 +671,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -663,7 +685,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -671,13 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -685,7 +707,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -693,13 +715,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -707,7 +729,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -715,13 +737,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -729,7 +751,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -737,13 +759,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -751,7 +773,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -759,13 +781,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -773,7 +795,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -781,13 +803,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -795,7 +817,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -803,13 +825,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -817,7 +839,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -825,13 +847,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -839,7 +861,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -847,13 +869,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -861,7 +883,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -869,13 +891,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -883,7 +905,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -891,13 +913,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -905,7 +927,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -913,13 +935,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -927,7 +949,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -935,13 +957,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -949,7 +971,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -957,13 +979,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -971,7 +993,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -979,13 +1001,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -993,7 +1015,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1001,13 +1023,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1015,7 +1037,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1023,13 +1045,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1037,7 +1059,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1045,13 +1067,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1059,7 +1081,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1067,13 +1089,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1081,7 +1103,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1089,13 +1111,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1103,7 +1125,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -1111,13 +1133,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1125,7 +1147,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1133,13 +1155,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1147,7 +1169,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1155,13 +1177,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1169,7 +1191,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1177,13 +1199,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -1191,7 +1213,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1199,13 +1221,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -1213,7 +1235,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -1221,13 +1243,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -1235,7 +1257,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1243,13 +1265,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -1257,7 +1279,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -1265,13 +1287,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -1279,7 +1301,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -1287,13 +1309,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -1301,7 +1323,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1309,13 +1331,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -1323,7 +1345,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1331,13 +1353,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -1345,7 +1367,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1353,13 +1375,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -1367,7 +1389,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -1375,13 +1397,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -1389,7 +1411,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1397,13 +1419,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1411,7 +1433,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1419,13 +1441,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1433,7 +1455,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1441,13 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1455,7 +1477,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1463,13 +1485,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1477,7 +1499,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1485,13 +1507,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1499,7 +1521,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1507,13 +1529,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1521,7 +1543,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1529,13 +1551,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1543,7 +1565,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1551,13 +1573,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1565,7 +1587,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1573,13 +1595,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1587,7 +1609,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1595,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1609,7 +1631,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1617,13 +1639,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1631,7 +1653,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1639,13 +1661,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1653,7 +1675,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1661,13 +1683,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1675,7 +1697,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1683,13 +1705,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1697,7 +1719,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1705,13 +1727,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1719,7 +1741,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1727,13 +1749,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1741,7 +1763,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1749,13 +1771,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1763,7 +1785,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1771,13 +1793,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1785,7 +1807,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1793,13 +1815,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1807,7 +1829,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1815,13 +1837,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1829,7 +1851,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1837,13 +1859,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1851,7 +1873,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1859,13 +1881,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1873,7 +1895,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1881,13 +1903,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1895,7 +1917,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1903,13 +1925,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1917,7 +1939,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1925,13 +1947,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1939,7 +1961,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1947,13 +1969,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1961,7 +1983,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1969,13 +1991,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1983,7 +2005,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1991,13 +2013,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2005,7 +2027,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2013,13 +2035,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2027,7 +2049,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2035,13 +2057,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2049,7 +2071,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -2057,13 +2079,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2071,7 +2093,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2079,13 +2101,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2093,7 +2115,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -2101,13 +2123,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -2115,7 +2137,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2123,13 +2145,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2137,7 +2159,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2145,13 +2167,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -2159,7 +2181,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2167,13 +2189,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2181,7 +2203,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2189,13 +2211,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2203,7 +2225,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2211,13 +2233,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2225,7 +2247,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -2233,13 +2255,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2247,7 +2269,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2255,13 +2277,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -2269,7 +2291,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2277,13 +2299,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2291,7 +2313,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2299,13 +2321,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2313,7 +2335,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2321,13 +2343,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -2335,7 +2357,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2343,13 +2365,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -2357,7 +2379,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -2365,17 +2387,17 @@
         </is>
       </c>
     </row>
-    <row r="86" customHeight="1">
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="1" t="n"/>
-    </row>
     <row r="87" customHeight="1">
-      <c r="B87" s="1" t="n"/>
+      <c r="B87" s="4" t="n"/>
       <c r="C87" s="1" t="n"/>
     </row>
     <row r="88" customHeight="1">
       <c r="B88" s="1" t="n"/>
       <c r="C88" s="1" t="n"/>
+    </row>
+    <row r="89" customHeight="1">
+      <c r="B89" s="1" t="n"/>
+      <c r="C89" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2388,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2416,10 +2438,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>02/05/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>2 3 0 7
+0 4 8 1
+6 2 6 8
+4 5 5 9</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/3864 (0.28%)
+✅ iBet: 11/208 (5.29%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -2427,20 +2470,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -2448,20 +2491,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -2469,20 +2512,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -2490,20 +2533,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -2511,20 +2554,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -2532,20 +2575,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -2553,20 +2596,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -2574,20 +2617,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -2595,20 +2638,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -2616,20 +2659,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -2637,20 +2680,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -2658,20 +2701,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -2679,20 +2722,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -2700,20 +2743,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -2721,20 +2764,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -2742,20 +2785,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -2763,20 +2806,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -2784,20 +2827,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -2805,20 +2848,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -2826,20 +2869,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -2847,20 +2890,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -2868,20 +2911,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -2889,20 +2932,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -2910,20 +2953,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -2931,20 +2974,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -2952,20 +2995,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -2973,20 +3016,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -2994,20 +3037,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -3015,20 +3058,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -3036,20 +3079,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -3057,20 +3100,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -3078,20 +3121,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -3099,20 +3142,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -3120,20 +3163,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -3141,20 +3184,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -3162,20 +3205,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -3183,20 +3226,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -3204,20 +3247,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -3225,20 +3268,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -3246,20 +3289,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -3267,20 +3310,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -3288,20 +3331,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -3309,20 +3352,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -3330,20 +3373,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -3351,20 +3394,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -3372,20 +3415,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -3393,20 +3436,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -3414,20 +3457,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -3435,20 +3478,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -3456,20 +3499,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -3477,20 +3520,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -3498,20 +3541,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -3519,20 +3562,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -3540,20 +3583,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -3561,20 +3604,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -3582,20 +3625,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -3603,20 +3646,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -3624,20 +3667,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -3645,20 +3688,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -3666,20 +3709,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -3687,20 +3730,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -3708,20 +3751,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -3729,20 +3772,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -3750,20 +3793,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -3771,20 +3814,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -3792,20 +3835,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -3813,20 +3856,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -3834,20 +3877,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -3855,20 +3898,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -3876,20 +3919,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -3897,20 +3940,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -3918,20 +3961,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -3939,20 +3982,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -3960,20 +4003,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -3981,20 +4024,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -4002,20 +4045,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -4023,20 +4066,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -4044,20 +4087,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -4065,20 +4108,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -4086,20 +4129,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -4107,20 +4150,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -4128,20 +4171,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -4149,20 +4192,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -4170,20 +4213,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -4191,20 +4234,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -4212,20 +4255,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -4233,20 +4276,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -4254,20 +4297,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -4275,20 +4318,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -4296,20 +4339,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -4317,20 +4360,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -4338,20 +4381,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -4359,20 +4402,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -4380,20 +4423,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -4401,20 +4444,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -4422,20 +4465,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -4443,20 +4486,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -4464,20 +4507,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -4485,20 +4528,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -4506,20 +4549,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -4527,20 +4570,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -4548,20 +4591,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -4569,20 +4612,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -4590,20 +4633,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -4611,20 +4654,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -4632,20 +4675,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -4653,20 +4696,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -4674,20 +4717,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -4695,20 +4738,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -4716,20 +4759,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -4737,20 +4780,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -4758,20 +4801,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -4779,20 +4822,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -4800,20 +4843,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -4821,20 +4864,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -4842,20 +4885,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -4863,20 +4906,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -4884,20 +4927,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -4905,20 +4948,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -4926,20 +4969,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -4947,20 +4990,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -4968,20 +5011,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -4989,20 +5032,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -5010,20 +5053,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -5031,20 +5074,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -5052,20 +5095,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -5073,20 +5116,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -5094,20 +5137,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -5115,20 +5158,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -5136,20 +5179,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -5157,20 +5200,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -5178,20 +5221,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -5199,20 +5242,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -5220,20 +5263,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -5241,20 +5284,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -5262,20 +5305,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -5283,16 +5326,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="1" t="n"/>
-      <c r="C139" s="1" t="n"/>
     </row>
     <row r="140">
       <c r="B140" s="1" t="n"/>
@@ -5304,6 +5343,7 @@
     </row>
     <row r="142">
       <c r="B142" s="1" t="n"/>
+      <c r="C142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="B143" s="1" t="n"/>
@@ -5379,6 +5419,9 @@
     </row>
     <row r="167">
       <c r="B167" s="1" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,10 +527,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06/05/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>3 4 1 7
+0 2 8 6
+2 5 9 4
+5 6 7 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -538,14 +553,21 @@
 5 1 7 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 7/226 (3.10%)
+▶ Direct: 7/4302 (0.16%)
+▶ Total Sets hit: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -553,7 +575,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -561,13 +583,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -575,7 +597,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -583,13 +605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -597,7 +619,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -605,13 +627,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -619,7 +641,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -627,13 +649,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -641,7 +663,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -649,13 +671,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -663,7 +685,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -671,13 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -685,7 +707,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -693,13 +715,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -707,7 +729,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -715,13 +737,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -729,7 +751,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -737,13 +759,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -751,7 +773,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -759,13 +781,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -773,7 +795,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -781,13 +803,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -795,7 +817,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -803,13 +825,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -817,7 +839,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -825,13 +847,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -839,7 +861,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -847,13 +869,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -861,7 +883,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -869,13 +891,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -883,7 +905,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -891,13 +913,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -905,7 +927,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -913,13 +935,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -927,7 +949,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -935,13 +957,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -949,7 +971,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -957,13 +979,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -971,7 +993,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -979,13 +1001,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -993,7 +1015,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1001,13 +1023,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -1015,7 +1037,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1023,13 +1045,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1037,7 +1059,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1045,13 +1067,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1059,7 +1081,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1067,13 +1089,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1081,7 +1103,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1089,13 +1111,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1103,7 +1125,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1111,13 +1133,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1125,7 +1147,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -1133,13 +1155,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1147,7 +1169,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1155,13 +1177,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1169,7 +1191,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1177,13 +1199,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1191,7 +1213,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1199,13 +1221,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -1213,7 +1235,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1221,13 +1243,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -1235,7 +1257,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -1243,13 +1265,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -1257,7 +1279,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1265,13 +1287,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -1279,7 +1301,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -1287,13 +1309,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -1301,7 +1323,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -1309,13 +1331,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -1323,7 +1345,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1331,13 +1353,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -1345,7 +1367,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1353,13 +1375,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -1367,7 +1389,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1375,13 +1397,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -1389,7 +1411,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -1397,13 +1419,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -1411,7 +1433,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1419,13 +1441,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1433,7 +1455,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1441,13 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1455,7 +1477,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1463,13 +1485,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1477,7 +1499,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1485,13 +1507,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1499,7 +1521,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1507,13 +1529,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1521,7 +1543,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1529,13 +1551,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1543,7 +1565,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1551,13 +1573,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1565,7 +1587,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1573,13 +1595,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1587,7 +1609,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1595,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1609,7 +1631,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1617,13 +1639,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1631,7 +1653,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1639,13 +1661,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1653,7 +1675,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1661,13 +1683,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1675,7 +1697,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1683,13 +1705,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1697,7 +1719,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1705,13 +1727,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1719,7 +1741,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1727,13 +1749,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1741,7 +1763,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1749,13 +1771,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1763,7 +1785,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1771,13 +1793,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1785,7 +1807,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1793,13 +1815,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1807,7 +1829,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1815,13 +1837,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1829,7 +1851,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1837,13 +1859,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1851,7 +1873,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1859,13 +1881,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1873,7 +1895,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1881,13 +1903,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1895,7 +1917,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1903,13 +1925,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1917,7 +1939,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1925,13 +1947,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1939,7 +1961,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1947,13 +1969,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1961,7 +1983,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1969,13 +1991,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -1983,7 +2005,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -1991,13 +2013,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2005,7 +2027,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2013,13 +2035,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2027,7 +2049,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2035,13 +2057,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2049,7 +2071,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2057,13 +2079,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2071,7 +2093,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -2079,13 +2101,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2093,7 +2115,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2101,13 +2123,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2115,7 +2137,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -2123,13 +2145,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -2137,7 +2159,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2145,13 +2167,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2159,7 +2181,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2167,13 +2189,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -2181,7 +2203,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2189,13 +2211,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2203,7 +2225,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2211,13 +2233,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2225,7 +2247,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2233,13 +2255,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2247,7 +2269,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -2255,13 +2277,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2269,7 +2291,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2277,13 +2299,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -2291,7 +2313,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2299,13 +2321,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2313,7 +2335,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2321,13 +2343,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2335,7 +2357,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2343,13 +2365,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -2357,7 +2379,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2365,13 +2387,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -2379,7 +2401,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -2387,17 +2409,17 @@
         </is>
       </c>
     </row>
-    <row r="87" customHeight="1">
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="1" t="n"/>
-    </row>
     <row r="88" customHeight="1">
-      <c r="B88" s="1" t="n"/>
+      <c r="B88" s="4" t="n"/>
       <c r="C88" s="1" t="n"/>
     </row>
     <row r="89" customHeight="1">
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="1" t="n"/>
+    </row>
+    <row r="90" customHeight="1">
+      <c r="B90" s="1" t="n"/>
+      <c r="C90" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2410,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2438,10 +2460,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>03/05/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>1 8 0 9
+4 2 9 3
+8 1 4 7
+6 6 3 5</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/3672 (0.30%)
+✅ iBet: 11/195 (5.64%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -2449,20 +2492,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -2470,20 +2513,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -2491,20 +2534,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -2512,20 +2555,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -2533,20 +2576,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -2554,20 +2597,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -2575,20 +2618,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -2596,20 +2639,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -2617,20 +2660,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -2638,20 +2681,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -2659,20 +2702,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -2680,20 +2723,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -2701,20 +2744,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -2722,20 +2765,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -2743,20 +2786,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -2764,20 +2807,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -2785,20 +2828,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -2806,20 +2849,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -2827,20 +2870,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -2848,20 +2891,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -2869,20 +2912,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -2890,20 +2933,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -2911,20 +2954,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -2932,20 +2975,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -2953,20 +2996,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -2974,20 +3017,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -2995,20 +3038,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -3016,20 +3059,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -3037,20 +3080,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -3058,20 +3101,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -3079,20 +3122,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -3100,20 +3143,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -3121,20 +3164,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -3142,20 +3185,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -3163,20 +3206,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -3184,20 +3227,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -3205,20 +3248,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -3226,20 +3269,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -3247,20 +3290,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -3268,20 +3311,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -3289,20 +3332,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -3310,20 +3353,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -3331,20 +3374,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -3352,20 +3395,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -3373,20 +3416,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -3394,20 +3437,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -3415,20 +3458,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -3436,20 +3479,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -3457,20 +3500,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -3478,20 +3521,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -3499,20 +3542,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -3520,20 +3563,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -3541,20 +3584,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -3562,20 +3605,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -3583,20 +3626,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -3604,20 +3647,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -3625,20 +3668,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -3646,20 +3689,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -3667,20 +3710,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -3688,20 +3731,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -3709,20 +3752,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -3730,20 +3773,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -3751,20 +3794,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -3772,20 +3815,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -3793,20 +3836,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -3814,20 +3857,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -3835,20 +3878,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -3856,20 +3899,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -3877,20 +3920,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -3898,20 +3941,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -3919,20 +3962,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -3940,20 +3983,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -3961,20 +4004,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -3982,20 +4025,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -4003,20 +4046,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -4024,20 +4067,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -4045,20 +4088,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -4066,20 +4109,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -4087,20 +4130,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -4108,20 +4151,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -4129,20 +4172,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -4150,20 +4193,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -4171,20 +4214,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -4192,20 +4235,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -4213,20 +4256,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -4234,20 +4277,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -4255,20 +4298,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -4276,20 +4319,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -4297,20 +4340,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -4318,20 +4361,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -4339,20 +4382,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -4360,20 +4403,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -4381,20 +4424,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -4402,20 +4445,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -4423,20 +4466,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -4444,20 +4487,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -4465,20 +4508,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -4486,20 +4529,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -4507,20 +4550,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -4528,20 +4571,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -4549,20 +4592,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -4570,20 +4613,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -4591,20 +4634,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -4612,20 +4655,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -4633,20 +4676,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -4654,20 +4697,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -4675,20 +4718,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -4696,20 +4739,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -4717,20 +4760,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -4738,20 +4781,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -4759,20 +4802,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -4780,20 +4823,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -4801,20 +4844,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -4822,20 +4865,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -4843,20 +4886,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -4864,20 +4907,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -4885,20 +4928,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -4906,20 +4949,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -4927,20 +4970,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -4948,20 +4991,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -4969,20 +5012,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -4990,20 +5033,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -5011,20 +5054,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -5032,20 +5075,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -5053,20 +5096,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -5074,20 +5117,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -5095,20 +5138,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -5116,20 +5159,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -5137,20 +5180,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -5158,20 +5201,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -5179,20 +5222,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -5200,20 +5243,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -5221,20 +5264,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -5242,20 +5285,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -5263,20 +5306,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -5284,20 +5327,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -5305,20 +5348,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -5326,16 +5369,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="1" t="n"/>
-      <c r="C140" s="1" t="n"/>
     </row>
     <row r="141">
       <c r="B141" s="1" t="n"/>
@@ -5347,6 +5386,7 @@
     </row>
     <row r="143">
       <c r="B143" s="1" t="n"/>
+      <c r="C143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="B144" s="1" t="n"/>
@@ -5422,6 +5462,9 @@
     </row>
     <row r="168">
       <c r="B168" s="1" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06/05/2026 (Wed)</t>
+          <t>09/05/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
@@ -542,10 +542,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06/05/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3 4 1 7
+0 2 8 6
+2 5 9 4
+5 6 7 0</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 7/208 (3.37%)
+▶ Direct: 7/3864 (0.18%)
+▶ Total Sets hit: 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -553,7 +575,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -561,13 +583,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -575,7 +597,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -583,13 +605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -597,7 +619,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -605,13 +627,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -619,7 +641,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -627,13 +649,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -641,7 +663,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -649,13 +671,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -663,7 +685,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -671,13 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -685,7 +707,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -693,13 +715,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -707,7 +729,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -715,13 +737,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -729,7 +751,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -737,13 +759,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -751,7 +773,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -759,13 +781,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -773,7 +795,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -781,13 +803,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -795,7 +817,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -803,13 +825,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -817,7 +839,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -825,13 +847,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -839,7 +861,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -847,13 +869,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -861,7 +883,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -869,13 +891,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -883,7 +905,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -891,13 +913,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -905,7 +927,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -913,13 +935,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -927,7 +949,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -935,13 +957,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -949,7 +971,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -957,13 +979,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -971,7 +993,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -979,13 +1001,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -993,7 +1015,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -1001,13 +1023,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1015,7 +1037,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1023,13 +1045,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -1037,7 +1059,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1045,13 +1067,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1059,7 +1081,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1067,13 +1089,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1081,7 +1103,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1089,13 +1111,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1103,7 +1125,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1111,13 +1133,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1125,7 +1147,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1133,13 +1155,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1147,7 +1169,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -1155,13 +1177,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1169,7 +1191,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1177,13 +1199,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1191,7 +1213,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1199,13 +1221,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1213,7 +1235,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1221,13 +1243,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -1235,7 +1257,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1243,13 +1265,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -1257,7 +1279,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -1265,13 +1287,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -1279,7 +1301,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1287,13 +1309,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -1301,7 +1323,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -1309,13 +1331,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -1323,7 +1345,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -1331,13 +1353,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -1345,7 +1367,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1353,13 +1375,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -1367,7 +1389,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1375,13 +1397,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -1389,7 +1411,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1397,13 +1419,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -1411,7 +1433,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -1419,13 +1441,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -1433,7 +1455,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1441,13 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1455,7 +1477,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1463,13 +1485,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1477,7 +1499,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1485,13 +1507,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1499,7 +1521,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1507,13 +1529,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1521,7 +1543,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1529,13 +1551,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1543,7 +1565,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1551,13 +1573,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1565,7 +1587,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1573,13 +1595,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1587,7 +1609,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1595,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1609,7 +1631,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1617,13 +1639,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1631,7 +1653,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1639,13 +1661,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1653,7 +1675,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1661,13 +1683,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1675,7 +1697,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1683,13 +1705,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1697,7 +1719,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1705,13 +1727,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1719,7 +1741,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1727,13 +1749,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1741,7 +1763,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1749,13 +1771,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1763,7 +1785,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1771,13 +1793,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1785,7 +1807,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1793,13 +1815,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1807,7 +1829,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1815,13 +1837,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1829,7 +1851,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1837,13 +1859,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1851,7 +1873,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1859,13 +1881,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1873,7 +1895,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1881,13 +1903,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1895,7 +1917,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1903,13 +1925,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1917,7 +1939,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1925,13 +1947,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1939,7 +1961,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1947,13 +1969,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1961,7 +1983,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1969,13 +1991,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1983,7 +2005,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1991,13 +2013,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2005,7 +2027,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -2013,13 +2035,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2027,7 +2049,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2035,13 +2057,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2049,7 +2071,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2057,13 +2079,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2071,7 +2093,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2079,13 +2101,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2093,7 +2115,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -2101,13 +2123,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2115,7 +2137,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2123,13 +2145,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2137,7 +2159,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -2145,13 +2167,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -2159,7 +2181,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2167,13 +2189,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2181,7 +2203,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2189,13 +2211,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -2203,7 +2225,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2211,13 +2233,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2225,7 +2247,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2233,13 +2255,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2247,7 +2269,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2255,13 +2277,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2269,7 +2291,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -2277,13 +2299,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2291,7 +2313,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2299,13 +2321,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -2313,7 +2335,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2321,13 +2343,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2335,7 +2357,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2343,13 +2365,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2357,7 +2379,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2365,13 +2387,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -2379,7 +2401,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2387,13 +2409,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -2401,7 +2423,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -2409,17 +2431,17 @@
         </is>
       </c>
     </row>
-    <row r="88" customHeight="1">
-      <c r="B88" s="4" t="n"/>
-      <c r="C88" s="1" t="n"/>
-    </row>
     <row r="89" customHeight="1">
-      <c r="B89" s="1" t="n"/>
+      <c r="B89" s="4" t="n"/>
       <c r="C89" s="1" t="n"/>
     </row>
     <row r="90" customHeight="1">
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="1" t="n"/>
+    </row>
+    <row r="91" customHeight="1">
+      <c r="B91" s="1" t="n"/>
+      <c r="C91" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2432,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C169"/>
+  <dimension ref="A1:C170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2460,10 +2482,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06/05/2026 (Wed)</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>8 7 9 2
+1 1 0 3
+6 6 4 5
+3 0 5 7</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 10/4302 (0.23%)
+✅ iBet: 10/226 (4.42%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -2471,20 +2514,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -2492,20 +2535,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -2513,20 +2556,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -2534,20 +2577,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -2555,20 +2598,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -2576,20 +2619,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -2597,20 +2640,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -2618,20 +2661,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -2639,20 +2682,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -2660,20 +2703,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -2681,20 +2724,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -2702,20 +2745,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -2723,20 +2766,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -2744,20 +2787,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -2765,20 +2808,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -2786,20 +2829,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -2807,20 +2850,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -2828,20 +2871,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -2849,20 +2892,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -2870,20 +2913,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -2891,20 +2934,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -2912,20 +2955,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -2933,20 +2976,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -2954,20 +2997,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -2975,20 +3018,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -2996,20 +3039,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -3017,20 +3060,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -3038,20 +3081,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -3059,20 +3102,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -3080,20 +3123,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -3101,20 +3144,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -3122,20 +3165,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -3143,20 +3186,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -3164,20 +3207,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -3185,20 +3228,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -3206,20 +3249,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -3227,20 +3270,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -3248,20 +3291,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -3269,20 +3312,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -3290,20 +3333,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -3311,20 +3354,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -3332,20 +3375,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -3353,20 +3396,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -3374,20 +3417,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -3395,20 +3438,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -3416,20 +3459,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -3437,20 +3480,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -3458,20 +3501,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -3479,20 +3522,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -3500,20 +3543,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -3521,20 +3564,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -3542,20 +3585,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -3563,20 +3606,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -3584,20 +3627,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -3605,20 +3648,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -3626,20 +3669,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -3647,20 +3690,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -3668,20 +3711,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -3689,20 +3732,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -3710,20 +3753,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -3731,20 +3774,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -3752,20 +3795,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -3773,20 +3816,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -3794,20 +3837,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -3815,20 +3858,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -3836,20 +3879,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -3857,20 +3900,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -3878,20 +3921,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -3899,20 +3942,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -3920,20 +3963,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -3941,20 +3984,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -3962,20 +4005,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -3983,20 +4026,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -4004,20 +4047,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -4025,20 +4068,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -4046,20 +4089,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -4067,20 +4110,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -4088,20 +4131,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -4109,20 +4152,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -4130,20 +4173,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -4151,20 +4194,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -4172,20 +4215,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
+      <c r="B85" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -4193,20 +4236,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -4214,20 +4257,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -4235,20 +4278,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -4256,20 +4299,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -4277,20 +4320,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -4298,20 +4341,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -4319,20 +4362,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -4340,20 +4383,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -4361,20 +4404,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -4382,20 +4425,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -4403,20 +4446,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -4424,20 +4467,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -4445,20 +4488,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -4466,20 +4509,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -4487,20 +4530,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -4508,20 +4551,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -4529,20 +4572,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -4550,20 +4593,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -4571,20 +4614,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -4592,20 +4635,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -4613,20 +4656,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -4634,20 +4677,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -4655,20 +4698,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -4676,20 +4719,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -4697,20 +4740,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -4718,20 +4761,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -4739,20 +4782,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -4760,20 +4803,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -4781,20 +4824,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -4802,20 +4845,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -4823,20 +4866,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -4844,20 +4887,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -4865,20 +4908,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -4886,20 +4929,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -4907,20 +4950,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -4928,20 +4971,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -4949,20 +4992,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -4970,20 +5013,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -4991,20 +5034,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -5012,20 +5055,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -5033,20 +5076,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -5054,20 +5097,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -5075,20 +5118,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -5096,20 +5139,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -5117,20 +5160,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -5138,20 +5181,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -5159,20 +5202,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -5180,20 +5223,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -5201,20 +5244,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -5222,20 +5265,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -5243,20 +5286,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -5264,20 +5307,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -5285,20 +5328,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -5306,20 +5349,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -5327,20 +5370,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -5348,20 +5391,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -5369,16 +5412,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="1" t="n"/>
-      <c r="C141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="B142" s="1" t="n"/>
@@ -5390,6 +5429,7 @@
     </row>
     <row r="144">
       <c r="B144" s="1" t="n"/>
+      <c r="C144" s="1" t="n"/>
     </row>
     <row r="145">
       <c r="B145" s="1" t="n"/>
@@ -5465,6 +5505,9 @@
     </row>
     <row r="169">
       <c r="B169" s="1" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,10 +527,25 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10/05/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>3 4 1 7
+0 2 8 6
+2 5 9 0
+5 6 7 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -538,14 +553,21 @@
 5 6 7 0</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 10/208 (4.81%)
+▶ Direct: 10/3864 (0.26%)
+▶ Total Sets hit: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -553,7 +575,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -561,13 +583,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -575,7 +597,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -583,13 +605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -597,7 +619,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -605,13 +627,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -619,7 +641,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -627,13 +649,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -641,7 +663,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -649,13 +671,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -663,7 +685,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -671,13 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -685,7 +707,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -693,13 +715,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -707,7 +729,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -715,13 +737,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -729,7 +751,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -737,13 +759,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -751,7 +773,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -759,13 +781,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -773,7 +795,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -781,13 +803,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -795,7 +817,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -803,13 +825,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -817,7 +839,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -825,13 +847,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -839,7 +861,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -847,13 +869,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -861,7 +883,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -869,13 +891,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -883,7 +905,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -891,13 +913,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -905,7 +927,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -913,13 +935,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -927,7 +949,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -935,13 +957,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -949,7 +971,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -957,13 +979,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -971,7 +993,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -979,13 +1001,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -993,7 +1015,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -1001,13 +1023,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1015,7 +1037,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -1023,13 +1045,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1037,7 +1059,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1045,13 +1067,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -1059,7 +1081,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1067,13 +1089,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1081,7 +1103,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1089,13 +1111,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1103,7 +1125,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1111,13 +1133,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1125,7 +1147,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1133,13 +1155,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1147,7 +1169,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1155,13 +1177,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1169,7 +1191,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -1177,13 +1199,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1191,7 +1213,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1199,13 +1221,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1213,7 +1235,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1221,13 +1243,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1235,7 +1257,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1243,13 +1265,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -1257,7 +1279,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1265,13 +1287,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -1279,7 +1301,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -1287,13 +1309,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -1301,7 +1323,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1309,13 +1331,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -1323,7 +1345,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -1331,13 +1353,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -1345,7 +1367,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -1353,13 +1375,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -1367,7 +1389,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1375,13 +1397,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -1389,7 +1411,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1397,13 +1419,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -1411,7 +1433,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1419,13 +1441,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -1433,7 +1455,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -1441,13 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -1455,7 +1477,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1463,13 +1485,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1477,7 +1499,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1485,13 +1507,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1499,7 +1521,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1507,13 +1529,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1521,7 +1543,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1529,13 +1551,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1543,7 +1565,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1551,13 +1573,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1565,7 +1587,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1573,13 +1595,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1587,7 +1609,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1595,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1609,7 +1631,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1617,13 +1639,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1631,7 +1653,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1639,13 +1661,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1653,7 +1675,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1661,13 +1683,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1675,7 +1697,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1683,13 +1705,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1697,7 +1719,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1705,13 +1727,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1719,7 +1741,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1727,13 +1749,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1741,7 +1763,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1749,13 +1771,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1763,7 +1785,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1771,13 +1793,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1785,7 +1807,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1793,13 +1815,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1807,7 +1829,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1815,13 +1837,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1829,7 +1851,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1837,13 +1859,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1851,7 +1873,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1859,13 +1881,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1873,7 +1895,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1881,13 +1903,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1895,7 +1917,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1903,13 +1925,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1917,7 +1939,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1925,13 +1947,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1939,7 +1961,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1947,13 +1969,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1961,7 +1983,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1969,13 +1991,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1983,7 +2005,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -1991,13 +2013,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -2005,7 +2027,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2013,13 +2035,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2027,7 +2049,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -2035,13 +2057,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2049,7 +2071,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2057,13 +2079,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2071,7 +2093,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2079,13 +2101,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2093,7 +2115,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2101,13 +2123,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2115,7 +2137,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -2123,13 +2145,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2137,7 +2159,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2145,13 +2167,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2159,7 +2181,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -2167,13 +2189,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -2181,7 +2203,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2189,13 +2211,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2203,7 +2225,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2211,13 +2233,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -2225,7 +2247,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2233,13 +2255,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2247,7 +2269,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2255,13 +2277,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2269,7 +2291,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2277,13 +2299,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2291,7 +2313,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -2299,13 +2321,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2313,7 +2335,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2321,13 +2343,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -2335,7 +2357,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2343,13 +2365,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2357,7 +2379,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2365,13 +2387,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2379,7 +2401,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2387,13 +2409,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -2401,7 +2423,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2409,13 +2431,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -2423,7 +2445,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -2431,17 +2453,17 @@
         </is>
       </c>
     </row>
-    <row r="89" customHeight="1">
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="1" t="n"/>
-    </row>
     <row r="90" customHeight="1">
-      <c r="B90" s="1" t="n"/>
+      <c r="B90" s="4" t="n"/>
       <c r="C90" s="1" t="n"/>
     </row>
     <row r="91" customHeight="1">
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="1" t="n"/>
+    </row>
+    <row r="92" customHeight="1">
+      <c r="B92" s="1" t="n"/>
+      <c r="C92" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2454,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C170"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2482,10 +2504,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>09/05/2026 (Sat)</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>3 8 7 9
+5 0 2 7
+1 3 5 0
+2 4 1 6</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 10/3828 (0.26%)
+✅ iBet: 10/205 (4.88%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -2493,20 +2536,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -2514,20 +2557,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -2535,20 +2578,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -2556,20 +2599,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -2577,20 +2620,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -2598,20 +2641,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -2619,20 +2662,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -2640,20 +2683,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -2661,20 +2704,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -2682,20 +2725,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -2703,20 +2746,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -2724,20 +2767,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -2745,20 +2788,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -2766,20 +2809,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -2787,20 +2830,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -2808,20 +2851,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -2829,20 +2872,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -2850,20 +2893,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -2871,20 +2914,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -2892,20 +2935,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -2913,20 +2956,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -2934,20 +2977,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -2955,20 +2998,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -2976,20 +3019,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -2997,20 +3040,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -3018,20 +3061,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -3039,20 +3082,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -3060,20 +3103,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -3081,20 +3124,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -3102,20 +3145,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -3123,20 +3166,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -3144,20 +3187,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -3165,20 +3208,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -3186,20 +3229,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -3207,20 +3250,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -3228,20 +3271,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -3249,20 +3292,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -3270,20 +3313,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -3291,20 +3334,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -3312,20 +3355,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -3333,20 +3376,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -3354,20 +3397,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -3375,20 +3418,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -3396,20 +3439,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -3417,20 +3460,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -3438,20 +3481,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -3459,20 +3502,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -3480,20 +3523,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -3501,20 +3544,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -3522,20 +3565,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -3543,20 +3586,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -3564,20 +3607,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -3585,20 +3628,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -3606,20 +3649,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -3627,20 +3670,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -3648,20 +3691,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -3669,20 +3712,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -3690,20 +3733,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -3711,20 +3754,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -3732,20 +3775,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -3753,20 +3796,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -3774,20 +3817,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -3795,20 +3838,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -3816,20 +3859,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -3837,20 +3880,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -3858,20 +3901,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -3879,20 +3922,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -3900,20 +3943,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -3921,20 +3964,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -3942,20 +3985,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -3963,20 +4006,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -3984,20 +4027,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -4005,20 +4048,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -4026,20 +4069,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -4047,20 +4090,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -4068,20 +4111,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -4089,20 +4132,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -4110,20 +4153,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -4131,20 +4174,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -4152,20 +4195,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -4173,20 +4216,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -4194,20 +4237,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -4215,20 +4258,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B86" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -4236,20 +4279,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -4257,20 +4300,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -4278,20 +4321,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -4299,20 +4342,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -4320,20 +4363,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -4341,20 +4384,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -4362,20 +4405,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -4383,20 +4426,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -4404,20 +4447,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -4425,20 +4468,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -4446,20 +4489,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -4467,20 +4510,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -4488,20 +4531,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -4509,20 +4552,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -4530,20 +4573,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -4551,20 +4594,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -4572,20 +4615,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -4593,20 +4636,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -4614,20 +4657,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -4635,20 +4678,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -4656,20 +4699,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -4677,20 +4720,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -4698,20 +4741,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -4719,20 +4762,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -4740,20 +4783,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -4761,20 +4804,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -4782,20 +4825,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -4803,20 +4846,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -4824,20 +4867,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -4845,20 +4888,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -4866,20 +4909,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -4887,20 +4930,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -4908,20 +4951,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -4929,20 +4972,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -4950,20 +4993,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -4971,20 +5014,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -4992,20 +5035,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -5013,20 +5056,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -5034,20 +5077,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -5055,20 +5098,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -5076,20 +5119,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -5097,20 +5140,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -5118,20 +5161,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -5139,20 +5182,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -5160,20 +5203,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -5181,20 +5224,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -5202,20 +5245,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -5223,20 +5266,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -5244,20 +5287,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -5265,20 +5308,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -5286,20 +5329,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -5307,20 +5350,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -5328,20 +5371,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -5349,20 +5392,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -5370,20 +5413,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -5391,20 +5434,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -5412,16 +5455,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="1" t="n"/>
-      <c r="C142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="B143" s="1" t="n"/>
@@ -5433,6 +5472,7 @@
     </row>
     <row r="145">
       <c r="B145" s="1" t="n"/>
+      <c r="C145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="B146" s="1" t="n"/>
@@ -5508,6 +5548,9 @@
     </row>
     <row r="170">
       <c r="B170" s="1" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10/05/2026 (Sun)</t>
+          <t>13/05/2026 (Wed)</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
@@ -542,10 +542,32 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
+          <t>10/05/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3 4 1 7
+0 2 8 6
+2 5 9 0
+5 6 7 1</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>▶ iBet: 6/217 (2.76%)
+▶ Direct: 6/4128 (0.15%)
+▶ Total Sets hit: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -553,7 +575,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -561,13 +583,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -575,7 +597,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -583,13 +605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -597,7 +619,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -605,13 +627,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -619,7 +641,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -627,13 +649,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -641,7 +663,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -649,13 +671,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -663,7 +685,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -671,13 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -685,7 +707,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -693,13 +715,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -707,7 +729,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -715,13 +737,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -729,7 +751,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -737,13 +759,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -751,7 +773,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -759,13 +781,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -773,7 +795,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -781,13 +803,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -795,7 +817,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -803,13 +825,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -817,7 +839,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -825,13 +847,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -839,7 +861,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -847,13 +869,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -861,7 +883,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -869,13 +891,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -883,7 +905,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -891,13 +913,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 3
@@ -905,7 +927,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -913,13 +935,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -927,7 +949,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 15/237 (6.33%)
 ▶ Direct: 15/4554 (0.33%)
@@ -935,13 +957,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 5
@@ -949,7 +971,7 @@
 6 8 9 0</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -957,13 +979,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -971,7 +993,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -979,13 +1001,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -993,7 +1015,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1001,13 +1023,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1015,7 +1037,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/208 (4.33%)
 ▶ Direct: 9/3864 (0.23%)
@@ -1023,13 +1045,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1037,7 +1059,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/208 (5.77%)
 ▶ Direct: 12/3864 (0.31%)
@@ -1045,13 +1067,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -1059,7 +1081,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -1067,13 +1089,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 6
@@ -1081,7 +1103,7 @@
 5 6 7 1</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -1089,13 +1111,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 6
@@ -1103,7 +1125,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1111,13 +1133,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1125,7 +1147,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1133,13 +1155,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1147,7 +1169,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -1155,13 +1177,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 5
@@ -1169,7 +1191,7 @@
 6 9 7 0</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1177,13 +1199,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1191,7 +1213,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 17/226 (7.52%)
 ▶ Direct: 17/4302 (0.40%)
@@ -1199,13 +1221,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>3 4 1 9
 0 2 8 5
@@ -1213,7 +1235,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1221,13 +1243,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1235,7 +1257,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1243,13 +1265,13 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>9 4 3 1
 0 2 1 5
@@ -1257,7 +1279,7 @@
 6 8 7 0</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1265,13 +1287,13 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>9 4 3 8
 0 2 1 5
@@ -1279,7 +1301,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1287,13 +1309,13 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B37" s="12" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>9 3 1 7
 0 2 8 5
@@ -1301,7 +1323,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/223 (3.59%)
 ▶ Direct: 8/4212 (0.19%)
@@ -1309,13 +1331,13 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>9 4 3 7
 0 2 8 5
@@ -1323,7 +1345,7 @@
 6 1 7 0</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1331,13 +1353,13 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>1 4 3 9
 3 2 8 6
@@ -1345,7 +1367,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/221 (4.07%)
 ▶ Direct: 9/4230 (0.21%)
@@ -1353,13 +1375,13 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>0 4 3 9
 3 2 7 6
@@ -1367,7 +1389,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/220 (5.45%)
 ▶ Direct: 12/4176 (0.29%)
@@ -1375,13 +1397,13 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B41" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>1 4 3 7
 3 2 7 6
@@ -1389,7 +1411,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/217 (5.07%)
 ▶ Direct: 11/4128 (0.27%)
@@ -1397,13 +1419,13 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 7 4
@@ -1411,7 +1433,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -1419,13 +1441,13 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B43" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 7 4
@@ -1433,7 +1455,7 @@
 5 6 0 1</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1441,13 +1463,13 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>6 4 3 7
 3 2 8 4
@@ -1455,7 +1477,7 @@
 5 9 7 1</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 14/237 (5.91%)
 ▶ Direct: 14/4554 (0.31%)
@@ -1463,13 +1485,13 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>0 4 3 7
 3 2 1 4
@@ -1477,7 +1499,7 @@
 5 9 6 8</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1485,13 +1507,13 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 7 4
@@ -1499,7 +1521,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1507,13 +1529,13 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 3 2 4 6
@@ -1521,7 +1543,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/226 (5.31%)
 ▶ Direct: 12/4302 (0.28%)
@@ -1529,13 +1551,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 4 6
@@ -1543,7 +1565,7 @@
 5 9 6 0</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/220 (5.00%)
 ▶ Direct: 11/4176 (0.26%)
@@ -1551,13 +1573,13 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1565,7 +1587,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1573,13 +1595,13 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>8 6 3 7
 0 2 1 4
@@ -1587,7 +1609,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -1595,13 +1617,13 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 6 4
@@ -1609,7 +1631,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -1617,13 +1639,13 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1631,7 +1653,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/220 (4.09%)
 ▶ Direct: 9/4176 (0.22%)
@@ -1639,13 +1661,13 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B53" s="12" t="inlineStr">
+      <c r="B54" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 8 4
@@ -1653,7 +1675,7 @@
 5 9 6 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -1661,13 +1683,13 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B55" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1675,7 +1697,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/221 (4.98%)
 ▶ Direct: 11/4230 (0.26%)
@@ -1683,13 +1705,13 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1697,7 +1719,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/221 (5.43%)
 ▶ Direct: 12/4230 (0.28%)
@@ -1705,13 +1727,13 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1719,7 +1741,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1727,13 +1749,13 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1741,7 +1763,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -1749,13 +1771,13 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B59" s="12" t="inlineStr">
         <is>
           <t>8 4 1 7
 0 2 8 4
@@ -1763,7 +1785,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1771,13 +1793,13 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B59" s="12" t="inlineStr">
+      <c r="B60" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1785,7 +1807,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/196 (5.10%)
 ▶ Direct: 10/3606 (0.28%)
@@ -1793,13 +1815,13 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B61" s="12" t="inlineStr">
         <is>
           <t>6 4 1 2
 0 2 8 4
@@ -1807,7 +1829,7 @@
 5 9 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/196 (4.08%)
 ▶ Direct: 8/3606 (0.22%)
@@ -1815,13 +1837,13 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B61" s="12" t="inlineStr">
+      <c r="B62" s="12" t="inlineStr">
         <is>
           <t>7 4 1 9
 0 2 8 4
@@ -1829,7 +1851,7 @@
 5 9 3 6</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1837,13 +1859,13 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B63" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1851,7 +1873,7 @@
 5 6 9 1</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1859,13 +1881,13 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="inlineStr">
+      <c r="B64" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1873,7 +1895,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -1881,13 +1903,13 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>8 4 1 9
 0 2 8 4
@@ -1895,7 +1917,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -1903,13 +1925,13 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="inlineStr">
+      <c r="B66" s="12" t="inlineStr">
         <is>
           <t>8 4 2 9
 0 2 1 4
@@ -1917,7 +1939,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -1925,13 +1947,13 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B67" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1939,7 +1961,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -1947,13 +1969,13 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="inlineStr">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>8 4 2 1
 0 2 1 6
@@ -1961,7 +1983,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/200 (4.00%)
 ▶ Direct: 8/3504 (0.23%)
@@ -1969,13 +1991,13 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -1983,7 +2005,7 @@
 5 6 0 4</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/211 (2.84%)
 ▶ Direct: 6/3756 (0.16%)
@@ -1991,13 +2013,13 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="inlineStr">
+      <c r="B70" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -2005,7 +2027,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2013,13 +2035,13 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B71" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 6
@@ -2027,7 +2049,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/226 (5.75%)
 ▶ Direct: 13/4302 (0.30%)
@@ -2035,13 +2057,13 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B72" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2049,7 +2071,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/205 (6.34%)
 ▶ Direct: 13/3828 (0.34%)
@@ -2057,13 +2079,13 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B73" s="12" t="inlineStr">
         <is>
           <t>8 7 2 1
 0 2 1 4
@@ -2071,7 +2093,7 @@
 5 3 0 6</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2079,13 +2101,13 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="inlineStr">
+      <c r="B74" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2093,7 +2115,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -2101,13 +2123,13 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B75" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2115,7 +2137,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/237 (4.64%)
 ▶ Direct: 11/4554 (0.24%)
@@ -2123,13 +2145,13 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="inlineStr">
+      <c r="B76" s="12" t="inlineStr">
         <is>
           <t>0 4 2 1
 3 2 1 4
@@ -2137,7 +2159,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/237 (4.22%)
 ▶ Direct: 10/4554 (0.22%)
@@ -2145,13 +2167,13 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2159,7 +2181,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 11/226 (4.87%)
 ▶ Direct: 11/4302 (0.26%)
@@ -2167,13 +2189,13 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="inlineStr">
+      <c r="B78" s="12" t="inlineStr">
         <is>
           <t>0 7 2 1
 3 2 1 4
@@ -2181,7 +2203,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 6/226 (2.65%)
 ▶ Direct: 6/4302 (0.14%)
@@ -2189,13 +2211,13 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B78" s="12" t="inlineStr">
+      <c r="B79" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 1 4
@@ -2203,7 +2225,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2211,13 +2233,13 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2225,7 +2247,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2233,13 +2255,13 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B81" s="12" t="inlineStr">
         <is>
           <t>6 4 2 7
 0 2 8 4
@@ -2247,7 +2269,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -2255,13 +2277,13 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B81" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>0 4 2 7
 3 2 8 4
@@ -2269,7 +2291,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2277,13 +2299,13 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="inlineStr">
+      <c r="B83" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2291,7 +2313,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2299,13 +2321,13 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B83" s="12" t="inlineStr">
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2313,7 +2335,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/237 (3.38%)
 ▶ Direct: 8/4554 (0.18%)
@@ -2321,13 +2343,13 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B84" s="12" t="inlineStr">
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2335,7 +2357,7 @@
 5 6 3 1</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2343,13 +2365,13 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B85" s="12" t="inlineStr">
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 1 4
@@ -2357,7 +2379,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -2365,13 +2387,13 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2379,7 +2401,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/237 (3.80%)
 ▶ Direct: 9/4554 (0.20%)
@@ -2387,13 +2409,13 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>0 4 2 8
 3 2 8 4
@@ -2401,7 +2423,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 12/237 (5.06%)
 ▶ Direct: 12/4554 (0.26%)
@@ -2409,13 +2431,13 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>4 7 2 8
 3 2 8 4
@@ -2423,7 +2445,7 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/237 (5.49%)
 ▶ Direct: 13/4554 (0.29%)
@@ -2431,13 +2453,13 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>1 4 2 9
 0 2 8 6
@@ -2445,7 +2467,7 @@
 5 3 7 8</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/195 (4.62%)
 ▶ Direct: 9/3672 (0.25%)
@@ -2453,17 +2475,17 @@
         </is>
       </c>
     </row>
-    <row r="90" customHeight="1">
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="1" t="n"/>
-    </row>
     <row r="91" customHeight="1">
-      <c r="B91" s="1" t="n"/>
+      <c r="B91" s="4" t="n"/>
       <c r="C91" s="1" t="n"/>
     </row>
     <row r="92" customHeight="1">
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="1" t="n"/>
+    </row>
+    <row r="93" customHeight="1">
+      <c r="B93" s="1" t="n"/>
+      <c r="C93" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2476,7 +2498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C171"/>
+  <dimension ref="A1:C172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2504,10 +2526,31 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
+          <t>10/05/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>0 9 7 1
+2 0 8 7
+6 5 1 9
+5 4 4 3</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>✅ Direct: 11/4128 (0.27%)
+✅ iBet: 11/217 (5.07%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>3 8 7 9
 5 0 2 7
@@ -2515,20 +2558,20 @@
 2 4 1 6</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3828 (0.26%)
 ✅ iBet: 10/205 (4.88%)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>8 7 9 2
 1 1 0 3
@@ -2536,20 +2579,20 @@
 3 0 5 7</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>1 8 0 9
 4 2 9 3
@@ -2557,20 +2600,20 @@
 6 6 3 5</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3672 (0.30%)
 ✅ iBet: 11/195 (5.64%)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2 3 0 7
 0 4 8 1
@@ -2578,20 +2621,20 @@
 4 5 5 9</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>8 4 6 3
 9 3 9 7
@@ -2599,20 +2642,20 @@
 6 1 1 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4230 (0.33%)
 ✅ iBet: 14/221 (6.33%)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>7 3 9 7
 9 2 3 6
@@ -2620,20 +2663,20 @@
 4 0 1 5</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4212 (0.36%)
 ✅ iBet: 15/223 (6.73%)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>8 0 2 7
 5 4 1 8
@@ -2641,20 +2684,20 @@
 6 7 4 3</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>1 8 9 7
 9 5 2 6
@@ -2662,20 +2705,20 @@
 2 4 8 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3936 (0.30%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>9 4 1 6
 6 8 2 0
@@ -2683,20 +2726,20 @@
 5 3 0 5</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3936 (0.25%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>8 2 9 7
 3 0 1 8
@@ -2704,20 +2747,20 @@
 9 6 5 4</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4554 (0.31%)
 ✅ iBet: 14/237 (5.91%)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>3 1 2 6
 7 8 4 3
@@ -2725,20 +2768,20 @@
 0 5 0 2</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3606 (0.33%)
 ✅ iBet: 12/196 (6.12%)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>5 2 4 9
 3 9 8 8
@@ -2746,20 +2789,20 @@
 7 1 3 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>8 6 3 5
 0 9 0 9
@@ -2767,20 +2810,20 @@
 6 1 7 1</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>7 9 0 3
 1 6 9 8
@@ -2788,20 +2831,20 @@
 2 7 1 5</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>0 1 6 4
 4 2 7 6
@@ -2809,20 +2852,20 @@
 8 9 8 3</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>4 1 6 2
 0 9 1 4
@@ -2830,20 +2873,20 @@
 7 8 5 0</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 6/4176 (0.14%)
 ✅ iBet: 6/220 (2.73%)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>5 0 5 2
 6 9 1 6
@@ -2851,20 +2894,20 @@
 8 7 4 3</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>29/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>9 1 6 4
 6 2 7 3
@@ -2872,20 +2915,20 @@
 5 7 8 1</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4128 (0.31%)
 ✅ iBet: 13/217 (5.99%)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>28/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>0 7 5 5
 8 0 1 6
@@ -2893,20 +2936,20 @@
 3 2 9 4</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>25/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>8 7 7 1
 1 4 6 3
@@ -2914,20 +2957,20 @@
 6 8 0 5</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3864 (0.28%)
 ✅ iBet: 11/208 (5.29%)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>22/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>9 2 4 8
 5 0 9 7
@@ -2935,20 +2978,20 @@
 2 6 0 1</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>21/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>3 2 1 7
 7 0 6 0
@@ -2956,20 +2999,20 @@
 8 4 2 3</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>18/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>2 3 5 9
 7 8 4 8
@@ -2977,20 +3020,20 @@
 6 5 1 6</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4230 (0.28%)
 ✅ iBet: 12/221 (5.43%)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>15/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>8 4 4 1
 6 6 9 7
@@ -2998,20 +3041,20 @@
 3 8 7 5</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>14/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>4 4 0 3
 9 8 1 1
@@ -3019,20 +3062,20 @@
 7 3 9 2</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>11/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>1 9 3 3
 0 7 4 7
@@ -3040,20 +3083,20 @@
 6 8 5 5</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>08/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>6 5 7 7
 0 3 3 6
@@ -3061,20 +3104,20 @@
 4 2 2 0</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>07/03/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>4 2 5 6
 9 3 8 3
@@ -3082,20 +3125,20 @@
 6 0 2 1</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>04/03/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>1 1 0 4
 3 2 9 8
@@ -3103,20 +3146,20 @@
 7 6 8 7</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" t="inlineStr">
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>01/03/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>7 6 9 7
 1 8 0 8
@@ -3124,20 +3167,20 @@
 0 3 1 4</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" t="inlineStr">
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>28/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>4 4 0 2
 0 1 3 1
@@ -3145,20 +3188,20 @@
 5 2 8 7</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" t="inlineStr">
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>25/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>8 4 1 6
 7 5 6 7
@@ -3166,20 +3209,20 @@
 4 1 2 9</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>22/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>1 2 1 0
 7 6 0 5
@@ -3187,20 +3230,20 @@
 6 4 9 3</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" t="inlineStr">
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>21/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>6 8 7 1
 2 0 1 9
@@ -3208,20 +3251,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3672 (0.25%)
 ✅ iBet: 9/195 (4.62%)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>18/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>4 4 0 8
 6 3 1 3
@@ -3229,20 +3272,20 @@
 9 6 9 7</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" t="inlineStr">
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>15/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>3 3 7 8
 9 0 4 0
@@ -3250,20 +3293,20 @@
 5 1 9 6</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" t="inlineStr">
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>14/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>9 6 6 1
 3 3 2 5
@@ -3271,20 +3314,20 @@
 5 8 0 7</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" t="inlineStr">
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" t="inlineStr">
         <is>
           <t>11/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>7 9 4 8
 2 0 8 7
@@ -3292,20 +3335,20 @@
 1 5 5 6</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" t="inlineStr">
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" t="inlineStr">
         <is>
           <t>08/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>3 5 1 9
 0 1 2 2
@@ -3313,20 +3356,20 @@
 6 4 4 7</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3864 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" t="inlineStr">
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" t="inlineStr">
         <is>
           <t>07/02/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>7 0 4 9
 1 2 3 6
@@ -3334,20 +3377,20 @@
 3 9 7 4</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" t="inlineStr">
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" t="inlineStr">
         <is>
           <t>04/02/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>0 3 9 1
 7 8 0 9
@@ -3355,20 +3398,20 @@
 4 2 4 5</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3672 (0.27%)
 ✅ iBet: 10/195 (5.13%)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t>01/02/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>9 9 3 6
 8 8 7 3
@@ -3376,20 +3419,20 @@
 6 5 1 2</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4230 (0.24%)
 ✅ iBet: 10/221 (4.52%)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" t="inlineStr">
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>31/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>6 2 3 5
 2 3 8 9
@@ -3397,20 +3440,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3936 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" t="inlineStr">
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" t="inlineStr">
         <is>
           <t>28/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>5 1 8 3
 6 6 1 7
@@ -3418,20 +3461,20 @@
 4 8 5 0</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3864 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" t="inlineStr">
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" t="inlineStr">
         <is>
           <t>25/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>3 7 3 9
 4 6 7 5
@@ -3439,20 +3482,20 @@
 0 9 6 1</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" t="inlineStr">
         <is>
           <t>24/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>0 5 7 7
 4 0 3 8
@@ -3460,20 +3503,20 @@
 2 4 5 6</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" t="inlineStr">
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" t="inlineStr">
         <is>
           <t>21/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>0 3 0 9
 9 7 4 8
@@ -3481,20 +3524,20 @@
 1 8 6 2</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" t="inlineStr">
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" t="inlineStr">
         <is>
           <t>18/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>5 3 9 7
 8 7 2 6
@@ -3502,20 +3545,20 @@
 4 8 1 0</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" t="inlineStr">
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" t="inlineStr">
         <is>
           <t>17/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>4 5 3 6
 3 7 1 5
@@ -3523,20 +3566,20 @@
 8 4 9 2</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" t="inlineStr">
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" t="inlineStr">
         <is>
           <t>14/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>0 7 1 5
 2 6 6 0
@@ -3544,20 +3587,20 @@
 3 1 9 8</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4230 (0.26%)
 ✅ iBet: 11/221 (4.98%)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" t="inlineStr">
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" t="inlineStr">
         <is>
           <t>11/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>0 5 8 5
 9 2 7 2
@@ -3565,20 +3608,20 @@
 8 0 6 3</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4230 (0.35%)
 ✅ iBet: 15/221 (6.79%)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" t="inlineStr">
         <is>
           <t>10/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>5 4 3 7
 0 9 6 8
@@ -3586,20 +3629,20 @@
 4 5 7 1</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 8/2688 (0.30%)
 ✅ iBet: 8/150 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" t="inlineStr">
         <is>
           <t>07/01/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>9 9 0 4
 7 3 7 6
@@ -3607,20 +3650,20 @@
 3 2 4 5</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" t="inlineStr">
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" t="inlineStr">
         <is>
           <t>04/01/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>9 5 9 3
 3 8 6 4
@@ -3628,20 +3671,20 @@
 6 4 7 2</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3828 (0.37%)
 ✅ iBet: 14/205 (6.83%)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" t="inlineStr">
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" t="inlineStr">
         <is>
           <t>03/01/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>7 3 0 3
 6 2 4 0
@@ -3649,20 +3692,20 @@
 5 1 8 1</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4230 (0.31%)
 ✅ iBet: 13/221 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" t="inlineStr">
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" t="inlineStr">
         <is>
           <t>31/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>2 8 3 6
 4 6 4 3
@@ -3670,20 +3713,20 @@
 0 1 8 5</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" t="inlineStr">
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" t="inlineStr">
         <is>
           <t>28/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>9 5 0 7
 3 8 3 4
@@ -3691,20 +3734,20 @@
 0 7 1 6</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 5/2688 (0.19%)
 ✅ iBet: 5/150 (3.33%)</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" t="inlineStr">
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" t="inlineStr">
         <is>
           <t>27/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>2 1 5 1
 8 3 8 5
@@ -3712,20 +3755,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4212 (0.33%)
 ✅ iBet: 14/223 (6.28%)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" t="inlineStr">
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" t="inlineStr">
         <is>
           <t>24/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>9 3 5 2
 8 2 6 9
@@ -3733,20 +3776,20 @@
 5 1 3 0</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4302 (0.35%)
 ✅ iBet: 15/226 (6.64%)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" t="inlineStr">
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" t="inlineStr">
         <is>
           <t>21/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>3 0 7 8
 5 8 9 7
@@ -3754,20 +3797,20 @@
 2 9 6 0</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" t="inlineStr">
         <is>
           <t>20/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>3 1 1 3
 7 8 4 5
@@ -3775,20 +3818,20 @@
 5 9 9 6</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3672 (0.33%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" t="inlineStr">
         <is>
           <t>17/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>8 4 9 6
 7 1 8 2
@@ -3796,20 +3839,20 @@
 2 5 6 4</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4302 (0.26%)
 ✅ iBet: 11/226 (4.87%)</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" t="inlineStr">
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>14/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>6 3 1 4
 7 0 5 5
@@ -3817,20 +3860,20 @@
 4 9 7 9</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4302 (0.30%)
 ✅ iBet: 13/226 (5.75%)</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" t="inlineStr">
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" t="inlineStr">
         <is>
           <t>13/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>8 4 8 9
 0 1 6 4
@@ -3838,20 +3881,20 @@
 5 6 2 3</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
+      <c r="C66" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4230 (0.21%)
 ✅ iBet: 9/221 (4.07%)</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" t="inlineStr">
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>10/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>9 7 1 9
 6 3 2 2
@@ -3859,20 +3902,20 @@
 5 4 6 3</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
+      <c r="C67" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4302 (0.21%)
 ✅ iBet: 9/226 (3.98%)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" t="inlineStr">
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" t="inlineStr">
         <is>
           <t>07/12/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>7 4 7 8
 2 5 9 5
@@ -3880,20 +3923,20 @@
 0 9 3 1</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/3672 (0.19%)
 ✅ iBet: 7/195 (3.59%)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" t="inlineStr">
         <is>
           <t>06/12/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>8 8 7 5
 1 7 4 3
@@ -3901,20 +3944,20 @@
 0 2 0 6</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3864 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" t="inlineStr">
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" t="inlineStr">
         <is>
           <t>03/12/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>9 8 3 1
 0 7 4 8
@@ -3922,20 +3965,20 @@
 6 5 7 2</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/4554 (0.37%)
 ✅ iBet: 17/237 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" t="inlineStr">
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" t="inlineStr">
         <is>
           <t>30/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>1 2 3 7
 6 3 9 6
@@ -3943,20 +3986,20 @@
 7 4 0 5</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3672 (0.35%)
 ✅ iBet: 13/195 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" t="inlineStr">
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>29/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>8 3 1 8
 2 7 4 6
@@ -3964,20 +4007,20 @@
 9 6 7 0</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4176 (0.24%)
 ✅ iBet: 10/220 (4.55%)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" t="inlineStr">
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>26/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>8 9 3 4
 5 2 7 6
@@ -3985,20 +4028,20 @@
 4 3 0 1</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 7/4176 (0.17%)
 ✅ iBet: 7/220 (3.18%)</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" t="inlineStr">
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>23/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>4 7 5 5
 7 3 2 0
@@ -4006,20 +4049,20 @@
 6 2 9 1</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4176 (0.36%)
 ✅ iBet: 15/220 (6.82%)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" t="inlineStr">
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>22/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>8 8 3 2
 5 7 7 4
@@ -4027,20 +4070,20 @@
 3 9 1 6</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3606 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" t="inlineStr">
         <is>
           <t>19/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>2 4 3 1
 8 7 1 3
@@ -4048,20 +4091,20 @@
 4 0 6 6</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3828 (0.24%)
 ✅ iBet: 9/205 (4.39%)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" t="inlineStr">
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" t="inlineStr">
         <is>
           <t>16/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B76" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>7 1 9 6
 1 4 6 8
@@ -4069,20 +4112,20 @@
 2 8 0 5</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/3672 (0.41%)
 ✅ iBet: 15/195 (7.69%)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" t="inlineStr">
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" t="inlineStr">
         <is>
           <t>15/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>8 7 0 1
 9 8 5 9
@@ -4090,20 +4133,20 @@
 1 2 6 3</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4128 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" t="inlineStr">
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" t="inlineStr">
         <is>
           <t>12/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>8 7 2 6
 3 8 1 3
@@ -4111,20 +4154,20 @@
 9 2 0 5</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4302 (0.33%)
 ✅ iBet: 14/226 (6.19%)</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" t="inlineStr">
         <is>
           <t>09/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B79" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>0 8 4 9
 9 5 1 7
@@ -4132,20 +4175,20 @@
 4 2 3 3</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4212 (0.24%)
 ✅ iBet: 10/223 (4.48%)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" t="inlineStr">
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" t="inlineStr">
         <is>
           <t>08/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>6 4 6 7
 0 2 0 5
@@ -4153,20 +4196,20 @@
 7 3 8 1</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 16/4212 (0.38%)
 ✅ iBet: 16/223 (7.17%)</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" t="inlineStr">
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" t="inlineStr">
         <is>
           <t>05/11/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B81" s="11" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>0 3 4 7
 2 7 8 1
@@ -4174,20 +4217,20 @@
 4 8 0 6</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4176 (0.29%)
 ✅ iBet: 12/220 (5.45%)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" t="inlineStr">
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" t="inlineStr">
         <is>
           <t>02/11/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>8 5 8 4
 0 2 6 7
@@ -4195,20 +4238,20 @@
 5 6 1 3</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3703 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" t="inlineStr">
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" t="inlineStr">
         <is>
           <t>01/11/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B83" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>9 3 2 3
 4 6 4 5
@@ -4216,20 +4259,20 @@
 0 2 7 1</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3818 (0.26%)
 ✅ iBet: 10/208 (4.81%)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" t="inlineStr">
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" t="inlineStr">
         <is>
           <t>29/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B84" s="11" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>3 0 5 1
 5 4 8 8
@@ -4237,20 +4280,20 @@
 6 7 7 9</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" t="inlineStr">
         <is>
           <t>26/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B85" s="11" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>7 8 4 8
 0 3 1 9
@@ -4258,20 +4301,20 @@
 4 9 5 2</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4128 (0.24%)
 ✅ iBet: 10/217 (4.61%)</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" t="inlineStr">
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" t="inlineStr">
         <is>
           <t>25/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>8 4 9 5
 6 8 7 8
@@ -4279,20 +4322,20 @@
 1 2 3 0</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3980 (0.30%)
 ✅ iBet: 12/215 (5.58%)</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" t="inlineStr">
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" t="inlineStr">
         <is>
           <t>22/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>0 6 4 2
 8 2 5 3
@@ -4300,20 +4343,20 @@
 5 1 9 7</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4554 (0.26%)
 ✅ iBet: 12/237 (5.06%)</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>19/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>8 6 4 8
 3 7 2 2
@@ -4321,20 +4364,20 @@
 1 4 3 0</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/4042 (0.32%)
 ✅ iBet: 13/216 (6.02%)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" t="inlineStr">
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" t="inlineStr">
         <is>
           <t>18/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>1 2 4 2
 2 0 8 6
@@ -4342,20 +4385,20 @@
 5 3 3 7</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
+      <c r="C90" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4078 (0.27%)
 ✅ iBet: 11/217 (5.07%)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" t="inlineStr">
         <is>
           <t>15/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>7 4 8 3
 0 3 7 2
@@ -4363,20 +4406,20 @@
 5 6 3 4</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" t="inlineStr">
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" t="inlineStr">
         <is>
           <t>12/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>9 7 7 9
 1 4 0 5
@@ -4384,20 +4427,20 @@
 2 8 3 6</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="60" customHeight="1">
-      <c r="A92" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" t="inlineStr">
         <is>
           <t>11/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>5 8 0 8
 0 2 7 5
@@ -4405,20 +4448,20 @@
 6 0 9 4</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
+      <c r="C93" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" t="inlineStr">
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" t="inlineStr">
         <is>
           <t>8/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>4 0 1 9
 8 9 2 4
@@ -4426,20 +4469,20 @@
 0 6 8 7</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4302 (0.23%)
 ✅ iBet: 10/226 (4.42%)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="60" customHeight="1">
-      <c r="A94" t="inlineStr">
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" t="inlineStr">
         <is>
           <t>5/10/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>4 2 4 4
 7 8 7 3
@@ -4447,20 +4490,20 @@
 5 1 3 6</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/188 (5.85%)</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" t="inlineStr">
         <is>
           <t>4/10/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>6 4 9 1
 9 6 3 0
@@ -4468,20 +4511,20 @@
 1 7 5 8</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3446 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" t="inlineStr">
         <is>
           <t>1/10/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>0 5 9 0
 8 0 6 5
@@ -4489,20 +4532,20 @@
 3 2 7 1</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4132 (0.29%)
 ✅ iBet: 12/219 (5.48%)</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" t="inlineStr">
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" t="inlineStr">
         <is>
           <t>28/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>5 9 5 8
 4 0 6 4
@@ -4510,20 +4553,20 @@
 1 3 7 2</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 17/3904 (0.44%)
 ✅ iBet: 17/209 (8.13%)</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="60" customHeight="1">
-      <c r="A98" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" t="inlineStr">
         <is>
           <t>27/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>0 8 8 9
 7 3 6 4
@@ -4531,20 +4574,20 @@
 9 7 5 1</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" t="inlineStr">
         <is>
           <t>24/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B99" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>3 0 2 1
 9 1 6 2
@@ -4552,20 +4595,20 @@
 0 3 5 4</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="60" customHeight="1">
-      <c r="A100" t="inlineStr">
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" t="inlineStr">
         <is>
           <t>21/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B100" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>6 7 2 5
 4 8 3 3
@@ -4573,20 +4616,20 @@
 8 9 1 0</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3980 (0.23%)
 ✅ iBet: 9/215 (4.19%)</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="60" customHeight="1">
-      <c r="A101" t="inlineStr">
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" t="inlineStr">
         <is>
           <t>20/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B101" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>7 6 3 3
 0 9 7 0
@@ -4594,20 +4637,20 @@
 5 8 4 1</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3841 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="60" customHeight="1">
-      <c r="A102" t="inlineStr">
+    <row r="103" ht="60" customHeight="1">
+      <c r="A103" t="inlineStr">
         <is>
           <t>17/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>3 7 4 7
 0 2 1 8
@@ -4615,20 +4658,20 @@
 6 1 9 5</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" t="inlineStr">
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" t="inlineStr">
         <is>
           <t>14/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B103" s="8" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>5 4 1 4
 8 0 8 5
@@ -4636,20 +4679,20 @@
 3 6 2 0</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4144 (0.36%)
 ✅ iBet: 15/222 (6.76%)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="60" customHeight="1">
-      <c r="A104" t="inlineStr">
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" t="inlineStr">
         <is>
           <t>13/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>1 2 2 6
 3 6 5 1
@@ -4657,20 +4700,20 @@
 7 3 4 0</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3544 (0.28%)
 ✅ iBet: 10/196 (5.10%)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="60" customHeight="1">
-      <c r="A105" t="inlineStr">
+    <row r="106" ht="60" customHeight="1">
+      <c r="A106" t="inlineStr">
         <is>
           <t>10/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>7 4 8 1
 9 2 1 8
@@ -4678,20 +4721,20 @@
 0 9 0 3</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3904 (0.26%)
 ✅ iBet: 10/209 (4.78%)</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="60" customHeight="1">
-      <c r="A106" t="inlineStr">
+    <row r="107" ht="60" customHeight="1">
+      <c r="A107" t="inlineStr">
         <is>
           <t>7/9/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>7 3 3 6
 3 0 6 5
@@ -4699,20 +4742,20 @@
 4 6 9 8</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="60" customHeight="1">
-      <c r="A107" t="inlineStr">
+    <row r="108" ht="60" customHeight="1">
+      <c r="A108" t="inlineStr">
         <is>
           <t>6/9/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>9 9 4 5
 0 2 1 7
@@ -4720,20 +4763,20 @@
 3 4 8 6</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3841 (0.23%)
 ✅ iBet: 9/209 (4.31%)</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="60" customHeight="1">
-      <c r="A108" t="inlineStr">
+    <row r="109" ht="60" customHeight="1">
+      <c r="A109" t="inlineStr">
         <is>
           <t>3/9/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>5 9 8 1
 0 4 1 0
@@ -4741,20 +4784,20 @@
 4 7 6 2</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3872 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" t="inlineStr">
+    <row r="110" ht="60" customHeight="1">
+      <c r="A110" t="inlineStr">
         <is>
           <t>31/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>0 0 0 7
 3 2 7 4
@@ -4762,20 +4805,20 @@
 1 1 6 9</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="60" customHeight="1">
-      <c r="A110" t="inlineStr">
+    <row r="111" ht="60" customHeight="1">
+      <c r="A111" t="inlineStr">
         <is>
           <t>30/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>9 8 6 8
 5 5 2 4
@@ -4783,20 +4826,20 @@
 7 9 9 0</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3904 (0.36%)
 ✅ iBet: 14/209 (6.70%)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" t="inlineStr">
+    <row r="112" ht="60" customHeight="1">
+      <c r="A112" t="inlineStr">
         <is>
           <t>27/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>6 0 6 5
 3 6 0 1
@@ -4804,20 +4847,20 @@
 8 8 2 9</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4042 (0.27%)
 ✅ iBet: 11/216 (5.09%)</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="60" customHeight="1">
-      <c r="A112" t="inlineStr">
+    <row r="113" ht="60" customHeight="1">
+      <c r="A113" t="inlineStr">
         <is>
           <t>24/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>6 1 2 7
 9 6 9 3
@@ -4825,20 +4868,20 @@
 3 9 5 0</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3904 (0.33%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="60" customHeight="1">
-      <c r="A113" t="inlineStr">
+    <row r="114" ht="60" customHeight="1">
+      <c r="A114" t="inlineStr">
         <is>
           <t>23/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>2 3 5 0
 0 2 2 6
@@ -4846,20 +4889,20 @@
 5 1 9 8</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3734 (0.35%)
 ✅ iBet: 13/204 (6.37%)</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="60" customHeight="1">
-      <c r="A114" t="inlineStr">
+    <row r="115" ht="60" customHeight="1">
+      <c r="A115" t="inlineStr">
         <is>
           <t>20/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>8 3 1 3
 3 2 3 2
@@ -4867,20 +4910,20 @@
 6 1 0 9</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3799 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="60" customHeight="1">
-      <c r="A115" t="inlineStr">
+    <row r="116" ht="60" customHeight="1">
+      <c r="A116" t="inlineStr">
         <is>
           <t>17/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>4 4 2 6
 5 7 0 7
@@ -4888,20 +4931,20 @@
 3 5 9 8</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="60" customHeight="1">
-      <c r="A116" t="inlineStr">
+    <row r="117" ht="60" customHeight="1">
+      <c r="A117" t="inlineStr">
         <is>
           <t>16/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>5 2 6 5
 2 6 4 4
@@ -4909,20 +4952,20 @@
 7 3 1 8</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3841 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="60" customHeight="1">
-      <c r="A117" t="inlineStr">
+    <row r="118" ht="60" customHeight="1">
+      <c r="A118" t="inlineStr">
         <is>
           <t>13/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>3 7 7 7
 0 9 9 0
@@ -4930,20 +4973,20 @@
 5 1 6 4</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4078 (0.34%)
 ✅ iBet: 14/217 (6.45%)</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="60" customHeight="1">
-      <c r="A118" t="inlineStr">
+    <row r="119" ht="60" customHeight="1">
+      <c r="A119" t="inlineStr">
         <is>
           <t>10/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>6 9 6 7
 5 4 5 2
@@ -4951,20 +4994,20 @@
 9 0 9 1</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3427 (0.32%)
 ✅ iBet: 11/192 (5.73%)</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="60" customHeight="1">
-      <c r="A119" t="inlineStr">
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" t="inlineStr">
         <is>
           <t>9/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>1 6 8 1
 3 0 5 7
@@ -4972,20 +5015,20 @@
 8 8 9 4</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3427 (0.26%)
 ✅ iBet: 9/192 (4.69%)</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="60" customHeight="1">
-      <c r="A120" t="inlineStr">
+    <row r="121" ht="60" customHeight="1">
+      <c r="A121" t="inlineStr">
         <is>
           <t>6/8/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>3 7 9 2
 2 5 3 1
@@ -4993,20 +5036,20 @@
 5 1 5 8</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3784 (0.29%)
 ✅ iBet: 11/204 (5.39%)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" t="inlineStr">
+    <row r="122" ht="60" customHeight="1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>3/8/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>9 3 2 2
 7 9 8 8
@@ -5014,20 +5057,20 @@
 6 8 4 0</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
+      <c r="C122" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3904 (0.31%)
 ✅ iBet: 12/209 (5.74%)</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="60" customHeight="1">
-      <c r="A122" t="inlineStr">
+    <row r="123" ht="60" customHeight="1">
+      <c r="A123" t="inlineStr">
         <is>
           <t>2/8/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>5 8 3 2
 8 3 8 4
@@ -5035,20 +5078,20 @@
 1 4 7 6</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
+      <c r="C123" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3872 (0.34%)
 ✅ iBet: 13/209 (6.22%)</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="60" customHeight="1">
-      <c r="A123" t="inlineStr">
+    <row r="124" ht="60" customHeight="1">
+      <c r="A124" t="inlineStr">
         <is>
           <t>30/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>2 1 2 4
 1 8 1 1
@@ -5056,20 +5099,20 @@
 4 5 6 0</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3353 (0.27%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="60" customHeight="1">
-      <c r="A124" t="inlineStr">
+    <row r="125" ht="60" customHeight="1">
+      <c r="A125" t="inlineStr">
         <is>
           <t>27/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>0 7 8 8
 4 6 0 6
@@ -5077,20 +5120,20 @@
 3 2 5 1</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 15/4240 (0.35%)
 ✅ iBet: 15/225 (6.67%)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" t="inlineStr">
+    <row r="126" ht="60" customHeight="1">
+      <c r="A126" t="inlineStr">
         <is>
           <t>26/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>0 3 7 4
 3 9 3 9
@@ -5098,20 +5141,20 @@
 2 8 1 6</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
+      <c r="C126" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3635 (0.39%)
 ✅ iBet: 14/201 (6.97%)</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="60" customHeight="1">
-      <c r="A126" t="inlineStr">
+    <row r="127" ht="60" customHeight="1">
+      <c r="A127" t="inlineStr">
         <is>
           <t>23/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B126" s="8" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>1 1 5 9
 5 5 4 3
@@ -5119,20 +5162,20 @@
 9 2 7 6</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
+      <c r="C127" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/3464 (0.29%)
 ✅ iBet: 10/192 (5.21%)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="60" customHeight="1">
-      <c r="A127" t="inlineStr">
+    <row r="128" ht="60" customHeight="1">
+      <c r="A128" t="inlineStr">
         <is>
           <t>20/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>2 8 1 9
 9 9 8 4
@@ -5140,20 +5183,20 @@
 4 3 0 6</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4132 (0.34%)
 ✅ iBet: 14/219 (6.39%)</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="60" customHeight="1">
-      <c r="A128" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" t="inlineStr">
         <is>
           <t>19/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>4 6 6 2
 9 8 4 3
@@ -5161,20 +5204,20 @@
 3 0 8 5</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/3828 (0.29%)
 ✅ iBet: 11/205 (5.37%)</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" t="inlineStr">
         <is>
           <t>16/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B129" s="8" t="inlineStr">
+      <c r="B130" s="8" t="inlineStr">
         <is>
           <t>9 1 1 2
 0 3 5 0
@@ -5182,20 +5225,20 @@
 5 6 8 4</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4240 (0.28%)
 ✅ iBet: 12/225 (5.33%)</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="60" customHeight="1">
-      <c r="A130" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" t="inlineStr">
         <is>
           <t>13/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>1 7 1 9
 4 5 9 0
@@ -5203,20 +5246,20 @@
 8 6 3 2</t>
         </is>
       </c>
-      <c r="C130" s="1" t="inlineStr">
+      <c r="C131" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3814 (0.31%)
 ✅ iBet: 12/208 (5.77%)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="60" customHeight="1">
-      <c r="A131" t="inlineStr">
+    <row r="132" ht="60" customHeight="1">
+      <c r="A132" t="inlineStr">
         <is>
           <t>12/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>1 0 8 9
 3 2 3 6
@@ -5224,20 +5267,20 @@
 5 6 7 2</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
+      <c r="C132" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 10/4240 (0.24%)
 ✅ iBet: 10/225 (4.44%)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="60" customHeight="1">
-      <c r="A132" t="inlineStr">
+    <row r="133" ht="60" customHeight="1">
+      <c r="A133" t="inlineStr">
         <is>
           <t>9/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>8 7 7 5
 1 3 8 6
@@ -5245,20 +5288,20 @@
 6 9 2 0</t>
         </is>
       </c>
-      <c r="C132" s="1" t="inlineStr">
+      <c r="C133" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/4042 (0.22%)
 ✅ iBet: 9/216 (4.17%)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="60" customHeight="1">
-      <c r="A133" t="inlineStr">
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" t="inlineStr">
         <is>
           <t>6/7/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>4 4 6 4
 2 9 1 6
@@ -5266,20 +5309,20 @@
 8 5 5 7</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
+      <c r="C134" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="60" customHeight="1">
-      <c r="A134" t="inlineStr">
+    <row r="135" ht="60" customHeight="1">
+      <c r="A135" t="inlineStr">
         <is>
           <t>5/7/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>0 1 9 2
 4 6 1 9
@@ -5287,20 +5330,20 @@
 3 9 8 5</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
+      <c r="C135" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3784 (0.32%)
 ✅ iBet: 12/204 (5.88%)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="60" customHeight="1">
-      <c r="A135" t="inlineStr">
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" t="inlineStr">
         <is>
           <t>2/7/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>6 4 1 8
 2 5 2 6
@@ -5308,20 +5351,20 @@
 5 6 3 0</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
+      <c r="C136" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/4042 (0.35%)
 ✅ iBet: 14/216 (6.48%)</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" t="inlineStr">
+    <row r="137" ht="60" customHeight="1">
+      <c r="A137" t="inlineStr">
         <is>
           <t>29/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>6 5 2 6
 4 0 7 9
@@ -5329,20 +5372,20 @@
 1 3 0 8</t>
         </is>
       </c>
-      <c r="C136" s="1" t="inlineStr">
+      <c r="C137" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="60" customHeight="1">
-      <c r="A137" t="inlineStr">
+    <row r="138" ht="60" customHeight="1">
+      <c r="A138" t="inlineStr">
         <is>
           <t>28/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>3 4 6 0
 4 9 3 6
@@ -5350,20 +5393,20 @@
 0 0 4 8</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 14/3980 (0.35%)
 ✅ iBet: 14/215 (6.51%)</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" t="inlineStr">
+    <row r="139" ht="60" customHeight="1">
+      <c r="A139" t="inlineStr">
         <is>
           <t>25/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>2 0 5 7
 6 2 8 8
@@ -5371,20 +5414,20 @@
 7 6 1 4</t>
         </is>
       </c>
-      <c r="C138" s="1" t="inlineStr">
+      <c r="C139" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/4302 (0.28%)
 ✅ iBet: 12/226 (5.31%)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="60" customHeight="1">
-      <c r="A139" t="inlineStr">
+    <row r="140" ht="60" customHeight="1">
+      <c r="A140" t="inlineStr">
         <is>
           <t>22/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>4 1 3 7
 6 2 5 4
@@ -5392,20 +5435,20 @@
 9 5 6 3</t>
         </is>
       </c>
-      <c r="C139" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 11/4144 (0.27%)
 ✅ iBet: 11/222 (4.95%)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="60" customHeight="1">
-      <c r="A140" t="inlineStr">
+    <row r="141" ht="60" customHeight="1">
+      <c r="A141" t="inlineStr">
         <is>
           <t>21/6/2025 (Sat)</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>4 6 1 8
 8 1 0 4
@@ -5413,20 +5456,20 @@
 0 2 9 3</t>
         </is>
       </c>
-      <c r="C140" s="1" t="inlineStr">
+      <c r="C141" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 13/3814 (0.34%)
 ✅ iBet: 13/208 (6.25%)</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="60" customHeight="1">
-      <c r="A141" t="inlineStr">
+    <row r="142" ht="60" customHeight="1">
+      <c r="A142" t="inlineStr">
         <is>
           <t>18/6/2025 (Wed)</t>
         </is>
       </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>2 1 2 1
 3 2 4 7
@@ -5434,20 +5477,20 @@
 5 3 3 8</t>
         </is>
       </c>
-      <c r="C141" s="1" t="inlineStr">
+      <c r="C142" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 9/3416 (0.26%)
 ✅ iBet: 9/188 (4.79%)</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="60" customHeight="1">
-      <c r="A142" t="inlineStr">
+    <row r="143" ht="60" customHeight="1">
+      <c r="A143" t="inlineStr">
         <is>
           <t>15/6/2025 (Sun)</t>
         </is>
       </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>2 9 3 2
 0 2 8 9
@@ -5455,16 +5498,12 @@
 6 7 4 1</t>
         </is>
       </c>
-      <c r="C142" s="1" t="inlineStr">
+      <c r="C143" s="1" t="inlineStr">
         <is>
           <t>✅ Direct: 12/3547 (0.34%)
 ✅ iBet: 12/195 (6.15%)</t>
         </is>
       </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="1" t="n"/>
-      <c r="C143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="B144" s="1" t="n"/>
@@ -5476,6 +5515,7 @@
     </row>
     <row r="146">
       <c r="B146" s="1" t="n"/>
+      <c r="C146" s="1" t="n"/>
     </row>
     <row r="147">
       <c r="B147" s="1" t="n"/>
@@ -5551,6 +5591,9 @@
     </row>
     <row r="171">
       <c r="B171" s="1" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/4d_box_output.xlsx
+++ b/4d_box_output.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13/05/2026 (Wed)</t>
+          <t>16/05/2026 (Sat)</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="3" ht="60" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10/05/2026 (Sun)</t>
+          <t>13/05/2026 (Wed)</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -555,19 +555,41 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>▶ iBet: 10/217 (4.61%)
+▶ Direct: 10/4128 (0.24%)
+▶ Total Sets hit: 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10/05/2026 (Sun)</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>3 4 1 7
+0 2 8 6
+2 5 9 0
+5 6 7 1</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
           <t>▶ iBet: 6/217 (2.76%)
 ▶ Direct: 6/4128 (0.15%)
 ▶ Total Sets hit: 6</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" t="inlineStr">
         <is>
           <t>09/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -575,7 +597,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -583,13 +605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" t="inlineStr">
         <is>
           <t>06/05/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -597,7 +619,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/208 (3.37%)
 ▶ Direct: 7/3864 (0.18%)
@@ -605,13 +627,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>03/05/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 8 6
@@ -619,7 +641,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/226 (3.10%)
 ▶ Direct: 7/4302 (0.16%)
@@ -627,13 +649,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>02/05/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -641,7 +663,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/226 (3.54%)
 ▶ Direct: 8/4302 (0.19%)
@@ -649,13 +671,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>29/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -663,7 +685,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/226 (4.42%)
 ▶ Direct: 10/4302 (0.23%)
@@ -671,13 +693,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>26/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -685,7 +707,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -693,13 +715,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>25/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -707,7 +729,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 5/226 (2.21%)
 ▶ Direct: 5/4302 (0.12%)
@@ -715,13 +737,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>22/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 4 6
@@ -729,7 +751,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 9/226 (3.98%)
 ▶ Direct: 9/4302 (0.21%)
@@ -737,13 +759,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>19/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -751,7 +773,7 @@
 5 6 7 0</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/208 (3.85%)
 ▶ Direct: 8/3864 (0.21%)
@@ -759,13 +781,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>18/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -773,7 +795,7 @@
 5 1 9 0</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 4/209 (1.91%)
 ▶ Direct: 4/3936 (0.10%)
@@ -781,13 +803,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>15/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -795,7 +817,7 @@
 5 1 7 0</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 7/220 (3.18%)
 ▶ Direct: 7/4176 (0.17%)
@@ -803,13 +825,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>12/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>8 4 3 7
 0 2 1 6
@@ -817,7 +839,7 @@
 5 9 7 0</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 8/220 (3.64%)
 ▶ Direct: 8/4176 (0.19%)
@@ -825,13 +847,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>11/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -839,7 +861,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 13/217 (5.99%)
 ▶ Direct: 13/4128 (0.31%)
@@ -847,13 +869,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>08/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>0 4 1 7
 3 2 7 6
@@ -861,7 +883,7 @@
 5 9 0 1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/217 (4.61%)
 ▶ Direct: 10/4128 (0.24%)
@@ -869,13 +891,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>05/04/2026 (Sun)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>3 4 1 7
 0 2 6 4
@@ -883,7 +905,7 @@
 5 8 7 0</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -891,13 +913,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>04/04/2026 (Sat)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>9 4 1 7
 0 2 6 3
@@ -905,7 +927,7 @@
 5 6 9 0</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>▶ iBet: 10/208 (4.81%)
 ▶ Direct: 10/3864 (0.26%)
@@ -913,13 +935,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>01/04/2026 (Wed)</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineSt